--- a/july 2026/STT Report Elite Marketing (20-06-26) (1).xlsx
+++ b/july 2026/STT Report Elite Marketing (20-06-26) (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61232DB7-A913-4004-846E-0C53DD043D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95F746D-993C-4986-B648-1E8F94085EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{4AEE6371-F34D-490E-9664-B5033CDC9B85}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="232">
   <si>
     <t>Date</t>
   </si>
@@ -554,6 +554,177 @@
   </si>
   <si>
     <t xml:space="preserve">Ali Park </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iqbal Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Brother </t>
+  </si>
+  <si>
+    <t>Tofail Store</t>
+  </si>
+  <si>
+    <t>Habibulah Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mubeen </t>
+  </si>
+  <si>
+    <t>Rehman Store</t>
+  </si>
+  <si>
+    <t>Al Kareem Society 60ft Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Falah Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">H Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sk Mart </t>
+  </si>
+  <si>
+    <t>Shera Store</t>
+  </si>
+  <si>
+    <t>Murad GS</t>
+  </si>
+  <si>
+    <t>Kamal Store</t>
+  </si>
+  <si>
+    <t>Umair Store</t>
+  </si>
+  <si>
+    <t>Gullberg 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS Mart </t>
+  </si>
+  <si>
+    <t>MF Chanda Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Us Mart </t>
+  </si>
+  <si>
+    <t>Shahdab Super Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Karam Smart Mart </t>
+  </si>
+  <si>
+    <t>Shahdab Colony</t>
+  </si>
+  <si>
+    <t>Trust Store</t>
+  </si>
+  <si>
+    <t>786 GS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groccer Mart </t>
+  </si>
+  <si>
+    <t>Bin Hadi Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Besta Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KS Mart </t>
+  </si>
+  <si>
+    <t>DHA</t>
+  </si>
+  <si>
+    <t>Shalimar Store</t>
+  </si>
+  <si>
+    <t>Sitara Bakers</t>
+  </si>
+  <si>
+    <t>Chelet Store</t>
+  </si>
+  <si>
+    <t>Askari Store</t>
+  </si>
+  <si>
+    <t>United Store</t>
+  </si>
+  <si>
+    <t>Classic Store</t>
+  </si>
+  <si>
+    <t>Cant Medical Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaheen Bakers </t>
+  </si>
+  <si>
+    <t>Saddar Bazaar</t>
+  </si>
+  <si>
+    <t>HK Mart</t>
+  </si>
+  <si>
+    <t>Husnain Store</t>
+  </si>
+  <si>
+    <t>Punjab Store</t>
+  </si>
+  <si>
+    <t>Malik Store</t>
+  </si>
+  <si>
+    <t>TK Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urban Mart </t>
+  </si>
+  <si>
+    <t>Ravi Store</t>
+  </si>
+  <si>
+    <t>Dua Book GS</t>
+  </si>
+  <si>
+    <t>Muhammad Sultan GS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Punjab Coprative </t>
+  </si>
+  <si>
+    <t>24/7</t>
+  </si>
+  <si>
+    <t>Afzal Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Captain Mart </t>
+  </si>
+  <si>
+    <t>Shanam Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smart Mart </t>
+  </si>
+  <si>
+    <t>Freshly Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marwa Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ali Mart </t>
+  </si>
+  <si>
+    <t>DHA Phase 5</t>
   </si>
 </sst>
 </file>
@@ -1463,22 +1634,22 @@
     <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1490,11 +1661,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1843,7 +2014,7 @@
     <col min="6" max="6" width="14.7265625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.7265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.26953125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.1796875" customWidth="1"/>
     <col min="12" max="13" width="8" bestFit="1" customWidth="1"/>
@@ -1874,44 +2045,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="3" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="108" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="108" t="s">
+      <c r="A1" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="109" t="s">
+      <c r="C1" s="104" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="109" t="s">
+      <c r="D1" s="104" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="109" t="s">
+      <c r="E1" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="109" t="s">
+      <c r="F1" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="108" t="s">
+      <c r="G1" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="109" t="s">
+      <c r="H1" s="104" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="56"/>
-      <c r="K1" s="108" t="s">
+      <c r="K1" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="113" t="s">
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="114"/>
-      <c r="R1" s="114"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
       <c r="S1" s="110" t="s">
         <v>10</v>
       </c>
@@ -1927,61 +2098,61 @@
       <c r="Y1" s="112"/>
       <c r="Z1" s="112"/>
       <c r="AA1" s="112"/>
-      <c r="AB1" s="106" t="s">
+      <c r="AB1" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="AC1" s="106" t="s">
+      <c r="AC1" s="108" t="s">
         <v>13</v>
       </c>
-      <c r="AD1" s="106" t="s">
+      <c r="AD1" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="AE1" s="106" t="s">
+      <c r="AE1" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="AF1" s="106" t="s">
+      <c r="AF1" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="AG1" s="106" t="s">
+      <c r="AG1" s="108" t="s">
         <v>17</v>
       </c>
       <c r="AH1" s="65">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AI1" s="106" t="s">
+      <c r="AI1" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="AJ1" s="106" t="s">
+      <c r="AJ1" s="108" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="106" t="s">
+      <c r="AK1" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="106" t="s">
+      <c r="AL1" s="108" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="106" t="s">
+      <c r="AM1" s="108" t="s">
         <v>22</v>
       </c>
-      <c r="AN1" s="104" t="s">
+      <c r="AN1" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="AO1" s="104" t="s">
+      <c r="AO1" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="AP1" s="106" t="s">
+      <c r="AP1" s="108" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:42" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="108"/>
-      <c r="B2" s="108"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="109"/>
+      <c r="A2" s="107"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="104"/>
       <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
@@ -2037,23 +2208,23 @@
       <c r="AA2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="107"/>
-      <c r="AC2" s="107"/>
-      <c r="AD2" s="107"/>
-      <c r="AE2" s="107"/>
-      <c r="AF2" s="107"/>
-      <c r="AG2" s="107"/>
+      <c r="AB2" s="109"/>
+      <c r="AC2" s="109"/>
+      <c r="AD2" s="109"/>
+      <c r="AE2" s="109"/>
+      <c r="AF2" s="109"/>
+      <c r="AG2" s="109"/>
       <c r="AH2" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="AI2" s="107"/>
-      <c r="AJ2" s="107"/>
-      <c r="AK2" s="107"/>
-      <c r="AL2" s="107"/>
-      <c r="AM2" s="107"/>
-      <c r="AN2" s="105"/>
-      <c r="AO2" s="105"/>
-      <c r="AP2" s="107"/>
+      <c r="AI2" s="109"/>
+      <c r="AJ2" s="109"/>
+      <c r="AK2" s="109"/>
+      <c r="AL2" s="109"/>
+      <c r="AM2" s="109"/>
+      <c r="AN2" s="114"/>
+      <c r="AO2" s="114"/>
+      <c r="AP2" s="109"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" s="71">
@@ -2064,7 +2235,7 @@
       </c>
       <c r="C3" s="103">
         <f ca="1">RAND()</f>
-        <v>0.69819085888065469</v>
+        <v>0.56310776061313506</v>
       </c>
       <c r="D3" s="73">
         <v>5643</v>
@@ -2198,7 +2369,7 @@
       </c>
       <c r="C4" s="103">
         <f t="shared" ref="C4:C67" ca="1" si="1">RAND()</f>
-        <v>3.218604671787384E-2</v>
+        <v>0.62396631997316698</v>
       </c>
       <c r="D4" s="73">
         <v>5464</v>
@@ -2332,7 +2503,7 @@
       </c>
       <c r="C5" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.14520506755301488</v>
+        <v>0.25965746637528908</v>
       </c>
       <c r="D5" s="73">
         <v>1523</v>
@@ -2466,7 +2637,7 @@
       </c>
       <c r="C6" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.14445139581337674</v>
+        <v>0.63775652524620274</v>
       </c>
       <c r="D6" s="73">
         <v>5461</v>
@@ -2600,7 +2771,7 @@
       </c>
       <c r="C7" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.93295525216932695</v>
+        <v>0.90565638849975705</v>
       </c>
       <c r="D7" s="73">
         <v>2316</v>
@@ -2743,7 +2914,7 @@
       </c>
       <c r="C8" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.41475143739256404</v>
+        <v>0.3871688293052149</v>
       </c>
       <c r="D8" s="73">
         <v>2084.3000000000002</v>
@@ -2875,7 +3046,7 @@
       </c>
       <c r="C9" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.95588790516449518</v>
+        <v>0.92132477118193745</v>
       </c>
       <c r="D9" s="73">
         <v>1418.6</v>
@@ -3007,7 +3178,7 @@
       </c>
       <c r="C10" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.16492400626307191</v>
+        <v>0.75414385764491265</v>
       </c>
       <c r="D10" s="73">
         <v>752.900000000001</v>
@@ -3138,7 +3309,7 @@
       </c>
       <c r="C11" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.18435047751512723</v>
+        <v>0.46458880885497977</v>
       </c>
       <c r="D11" s="73">
         <v>87.199999999999804</v>
@@ -3269,7 +3440,7 @@
       </c>
       <c r="C12" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85937874930248603</v>
+        <v>0.2864859038405233</v>
       </c>
       <c r="D12" s="73">
         <v>578.5</v>
@@ -3400,7 +3571,7 @@
       </c>
       <c r="C13" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.45115984084368654</v>
+        <v>0.6332715138054148</v>
       </c>
       <c r="D13" s="73">
         <v>1244.2</v>
@@ -3531,7 +3702,7 @@
       </c>
       <c r="C14" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.13917348576200672</v>
+        <v>0.34698198922115853</v>
       </c>
       <c r="D14" s="73">
         <v>1909.9</v>
@@ -3662,7 +3833,7 @@
       </c>
       <c r="C15" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.81045289310023183</v>
+        <v>0.50306898372798092</v>
       </c>
       <c r="D15" s="73">
         <v>2575.6</v>
@@ -3785,11 +3956,22 @@
       <c r="AP15" s="12"/>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A16" s="71"/>
-      <c r="B16" s="72"/>
-      <c r="C16" s="73"/>
-      <c r="D16" s="73"/>
-      <c r="E16" s="62"/>
+      <c r="A16" s="71">
+        <v>46204</v>
+      </c>
+      <c r="B16" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="103">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.41687825950101365</v>
+      </c>
+      <c r="D16" s="73">
+        <v>2575.6</v>
+      </c>
+      <c r="E16" s="62" t="s">
+        <v>87</v>
+      </c>
       <c r="F16" s="73" t="s">
         <v>109</v>
       </c>
@@ -3905,7 +4087,7 @@
       </c>
       <c r="C17" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.45297881161358455</v>
+        <v>0.77125080932682755</v>
       </c>
       <c r="D17" s="73">
         <v>2215.5571428571402</v>
@@ -4028,7 +4210,7 @@
       </c>
       <c r="C18" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.97129346258929361</v>
+        <v>0.83354235350450034</v>
       </c>
       <c r="D18" s="73">
         <v>2463.4857142857099</v>
@@ -4155,7 +4337,7 @@
       </c>
       <c r="C19" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.21996543842352068</v>
+        <v>0.63378668539940741</v>
       </c>
       <c r="D19" s="73">
         <v>2711.4142857142801</v>
@@ -4282,7 +4464,7 @@
       </c>
       <c r="C20" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.85662534494086828</v>
+        <v>0.38378981737237727</v>
       </c>
       <c r="D20" s="73">
         <v>2959.3428571428499</v>
@@ -4413,7 +4595,7 @@
       </c>
       <c r="C21" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.11486243478892377</v>
+        <v>0.41191561532924748</v>
       </c>
       <c r="D21" s="73">
         <v>3207.2714285714301</v>
@@ -4538,7 +4720,7 @@
       </c>
       <c r="C22" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.38082534149879532</v>
+        <v>0.29700964744122627</v>
       </c>
       <c r="D22" s="73">
         <v>3455.2</v>
@@ -4665,7 +4847,7 @@
       </c>
       <c r="C23" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.22989802599510223</v>
+        <v>0.36158575586947117</v>
       </c>
       <c r="D23" s="73">
         <v>3703.12857142857</v>
@@ -4780,11 +4962,22 @@
       <c r="AP23" s="12"/>
     </row>
     <row r="24" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A24" s="71"/>
-      <c r="B24" s="72"/>
-      <c r="C24" s="73"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="62"/>
+      <c r="A24" s="71">
+        <v>46204</v>
+      </c>
+      <c r="B24" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="103">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.58321692967159533</v>
+      </c>
+      <c r="D24" s="73">
+        <v>3703.12857142857</v>
+      </c>
+      <c r="E24" s="62" t="s">
+        <v>87</v>
+      </c>
       <c r="F24" s="73" t="s">
         <v>109</v>
       </c>
@@ -4904,7 +5097,7 @@
       </c>
       <c r="C25" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.33506957179415708</v>
+        <v>0.64107178929700104</v>
       </c>
       <c r="D25" s="73">
         <v>3951.0571428571402</v>
@@ -5027,7 +5220,7 @@
       </c>
       <c r="C26" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.35896282894052989</v>
+        <v>0.15346473989216769</v>
       </c>
       <c r="D26" s="73">
         <v>4198.9857142857099</v>
@@ -5152,7 +5345,7 @@
       </c>
       <c r="C27" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.22233603342393227</v>
+        <v>0.26872527698724169</v>
       </c>
       <c r="D27" s="73">
         <v>4446.9142857142797</v>
@@ -5275,7 +5468,7 @@
       </c>
       <c r="C28" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.44196081283013289</v>
+        <v>0.91587536961868843</v>
       </c>
       <c r="D28" s="73">
         <v>4694.8428571428503</v>
@@ -5402,7 +5595,7 @@
       </c>
       <c r="C29" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.36851511897858968</v>
+        <v>0.59093070354995414</v>
       </c>
       <c r="D29" s="73">
         <v>4942.7714285714301</v>
@@ -5527,7 +5720,7 @@
       </c>
       <c r="C30" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.32059855057556186</v>
+        <v>0.42995644089415719</v>
       </c>
       <c r="D30" s="73">
         <v>5190.7</v>
@@ -5650,7 +5843,7 @@
       </c>
       <c r="C31" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.11237012455899298</v>
+        <v>0.54500939144572413</v>
       </c>
       <c r="D31" s="73">
         <v>5438.6285714285696</v>
@@ -5765,11 +5958,22 @@
       <c r="AP31" s="12"/>
     </row>
     <row r="32" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A32" s="71"/>
-      <c r="B32" s="72"/>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
-      <c r="E32" s="62"/>
+      <c r="A32" s="71">
+        <v>46204</v>
+      </c>
+      <c r="B32" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="103">
+        <f t="shared" ca="1" si="1"/>
+        <v>0.28322826398386769</v>
+      </c>
+      <c r="D32" s="73">
+        <v>5438.6285714285696</v>
+      </c>
+      <c r="E32" s="62" t="s">
+        <v>87</v>
+      </c>
       <c r="F32" s="73" t="s">
         <v>110</v>
       </c>
@@ -5885,7 +6089,7 @@
       </c>
       <c r="C33" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84616306986549061</v>
+        <v>0.28383770843467326</v>
       </c>
       <c r="D33" s="73">
         <v>5686.5571428571402</v>
@@ -6018,7 +6222,7 @@
       </c>
       <c r="C34" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.40399021151543479</v>
+        <v>0.91123474941940286</v>
       </c>
       <c r="D34" s="73">
         <v>5934.4857142857099</v>
@@ -6141,7 +6345,7 @@
       </c>
       <c r="C35" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75603522645279386</v>
+        <v>0.83761352489318153</v>
       </c>
       <c r="D35" s="73">
         <v>6182.4142857142797</v>
@@ -6264,7 +6468,7 @@
       </c>
       <c r="C36" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.71930524159796072</v>
+        <v>0.3948777162698045</v>
       </c>
       <c r="D36" s="73">
         <v>6430.3428571428503</v>
@@ -6393,7 +6597,7 @@
       </c>
       <c r="C37" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.13811277992639259</v>
+        <v>0.41425456113347181</v>
       </c>
       <c r="D37" s="73">
         <v>6678.2714285714201</v>
@@ -6520,7 +6724,7 @@
       </c>
       <c r="C38" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.36316320396542867</v>
+        <v>3.4906795755411224E-2</v>
       </c>
       <c r="D38" s="73">
         <v>6926.2</v>
@@ -6647,7 +6851,7 @@
       </c>
       <c r="C39" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.9673203062112038</v>
+        <v>0.92893216928444222</v>
       </c>
       <c r="D39" s="73">
         <v>6926.2</v>
@@ -6780,7 +6984,7 @@
       </c>
       <c r="C40" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.77473318413507564</v>
+        <v>0.19182664294436613</v>
       </c>
       <c r="D40" s="73">
         <v>6926.2</v>
@@ -6909,7 +7113,7 @@
       </c>
       <c r="C41" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.23001448293454452</v>
+        <v>0.79524038071647729</v>
       </c>
       <c r="D41" s="73">
         <v>6926.2</v>
@@ -7036,7 +7240,7 @@
       </c>
       <c r="C42" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.98422872052772947</v>
+        <v>0.14361428133539456</v>
       </c>
       <c r="D42" s="73">
         <v>6926.2</v>
@@ -7161,7 +7365,7 @@
       </c>
       <c r="C43" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.12844879490035754</v>
+        <v>0.60715233736673457</v>
       </c>
       <c r="D43" s="73">
         <v>6926.2</v>
@@ -7284,7 +7488,7 @@
       </c>
       <c r="C44" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.10370250293992789</v>
+        <v>1.6905485175367496E-2</v>
       </c>
       <c r="D44" s="73">
         <v>6926.2</v>
@@ -7417,7 +7621,7 @@
       </c>
       <c r="C45" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.43029943601101028</v>
+        <v>0.51273775977807734</v>
       </c>
       <c r="D45" s="73">
         <v>6926.2</v>
@@ -7544,7 +7748,7 @@
       </c>
       <c r="C46" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.67425289998004934</v>
+        <v>0.63631280672856072</v>
       </c>
       <c r="D46" s="73">
         <v>6926.2</v>
@@ -7671,7 +7875,7 @@
       </c>
       <c r="C47" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.13841331327383455</v>
+        <v>0.14643347764137182</v>
       </c>
       <c r="D47" s="73">
         <v>6926.2</v>
@@ -7796,7 +8000,7 @@
       </c>
       <c r="C48" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.14705114789794538</v>
+        <v>0.5761502208847844</v>
       </c>
       <c r="D48" s="73">
         <v>6926.2</v>
@@ -7923,7 +8127,7 @@
       </c>
       <c r="C49" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.30435516730826728</v>
+        <v>0.60889556747259077</v>
       </c>
       <c r="D49" s="73">
         <v>6926.2</v>
@@ -8046,7 +8250,7 @@
       </c>
       <c r="C50" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84024975271558755</v>
+        <v>0.96483133577555724</v>
       </c>
       <c r="D50" s="73">
         <v>6926.2</v>
@@ -8173,7 +8377,7 @@
       </c>
       <c r="C51" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.60052407321017343</v>
+        <v>0.57559421619438922</v>
       </c>
       <c r="D51" s="73">
         <v>6926.2</v>
@@ -8306,7 +8510,7 @@
       </c>
       <c r="C52" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.89122054596445388</v>
+        <v>0.6963735496840735</v>
       </c>
       <c r="D52" s="73">
         <v>6926.2</v>
@@ -8435,7 +8639,7 @@
       </c>
       <c r="C53" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82845580301257216</v>
+        <v>0.52927115067152419</v>
       </c>
       <c r="D53" s="73">
         <v>6926.2</v>
@@ -8566,7 +8770,7 @@
       </c>
       <c r="C54" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.2595836116613538</v>
+        <v>0.47252574609259568</v>
       </c>
       <c r="D54" s="73">
         <v>6926.2</v>
@@ -8699,7 +8903,7 @@
       </c>
       <c r="C55" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.66679190786380449</v>
+        <v>0.47428935228118618</v>
       </c>
       <c r="D55" s="73">
         <v>6926.2</v>
@@ -8832,7 +9036,7 @@
       </c>
       <c r="C56" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.63156220650892492</v>
+        <v>0.45324627336989387</v>
       </c>
       <c r="D56" s="73">
         <v>6926.2</v>
@@ -8965,7 +9169,7 @@
       </c>
       <c r="C57" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.74708253318908002</v>
+        <v>0.14958040677756168</v>
       </c>
       <c r="D57" s="73">
         <v>6926.2</v>
@@ -9088,7 +9292,7 @@
       </c>
       <c r="C58" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.75197046092153719</v>
+        <v>0.77491906563236257</v>
       </c>
       <c r="D58" s="73">
         <v>6926.2</v>
@@ -9213,7 +9417,7 @@
       </c>
       <c r="C59" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>2.738031303584143E-2</v>
+        <v>0.67688444764886335</v>
       </c>
       <c r="D59" s="73">
         <v>6926.2</v>
@@ -9336,7 +9540,7 @@
       </c>
       <c r="C60" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.23588508680191478</v>
+        <v>0.54794564885145058</v>
       </c>
       <c r="D60" s="73">
         <v>6926.2</v>
@@ -9459,7 +9663,7 @@
       </c>
       <c r="C61" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.70777855827141445</v>
+        <v>0.93364672330197196</v>
       </c>
       <c r="D61" s="73">
         <v>6926.2</v>
@@ -9582,7 +9786,7 @@
       </c>
       <c r="C62" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.64965017947880754</v>
+        <v>0.43055033341169702</v>
       </c>
       <c r="D62" s="73">
         <v>6926.2</v>
@@ -9705,7 +9909,7 @@
       </c>
       <c r="C63" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.33134427277845357</v>
+        <v>0.59936730481142697</v>
       </c>
       <c r="D63" s="73">
         <v>6926.2</v>
@@ -9828,7 +10032,7 @@
       </c>
       <c r="C64" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.66824606132465647</v>
+        <v>0.18532631660636234</v>
       </c>
       <c r="D64" s="73">
         <v>6926.2</v>
@@ -9951,7 +10155,7 @@
       </c>
       <c r="C65" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.82305471459656299</v>
+        <v>0.23928956717638483</v>
       </c>
       <c r="D65" s="73">
         <v>6926.2</v>
@@ -10074,7 +10278,7 @@
       </c>
       <c r="C66" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.76956822780926115</v>
+        <v>0.81228722302991951</v>
       </c>
       <c r="D66" s="73">
         <v>6926.2</v>
@@ -10199,7 +10403,7 @@
       </c>
       <c r="C67" s="103">
         <f t="shared" ca="1" si="1"/>
-        <v>0.49904105158647161</v>
+        <v>0.32366773052376263</v>
       </c>
       <c r="D67" s="73">
         <v>6926.2</v>
@@ -10325,8 +10529,8 @@
         <v>86</v>
       </c>
       <c r="C68" s="103">
-        <f t="shared" ref="C68:C73" ca="1" si="55">RAND()</f>
-        <v>0.99839459510578388</v>
+        <f t="shared" ref="C68:C129" ca="1" si="55">RAND()</f>
+        <v>0.79470555434966728</v>
       </c>
       <c r="D68" s="73">
         <v>6926.2</v>
@@ -10453,7 +10657,7 @@
       </c>
       <c r="C69" s="103">
         <f t="shared" ca="1" si="55"/>
-        <v>0.29055011660208496</v>
+        <v>0.72783232730374592</v>
       </c>
       <c r="D69" s="73">
         <v>6926.2</v>
@@ -10586,7 +10790,7 @@
       </c>
       <c r="C70" s="103">
         <f t="shared" ca="1" si="55"/>
-        <v>0.63080647686906877</v>
+        <v>0.88741774815509311</v>
       </c>
       <c r="D70" s="73">
         <v>6926.2</v>
@@ -10717,7 +10921,7 @@
       </c>
       <c r="C71" s="103">
         <f t="shared" ca="1" si="55"/>
-        <v>0.83892055062165738</v>
+        <v>0.33183899086068558</v>
       </c>
       <c r="D71" s="73">
         <v>6926.2</v>
@@ -10840,7 +11044,7 @@
       </c>
       <c r="C72" s="103">
         <f t="shared" ca="1" si="55"/>
-        <v>0.69335506501421573</v>
+        <v>0.13016569569765479</v>
       </c>
       <c r="D72" s="73">
         <v>6926.2</v>
@@ -10963,7 +11167,7 @@
       </c>
       <c r="C73" s="103">
         <f t="shared" ca="1" si="55"/>
-        <v>0.47327368763169919</v>
+        <v>0.79474850010206621</v>
       </c>
       <c r="D73" s="73">
         <v>6926.2</v>
@@ -11081,14 +11285,31 @@
       <c r="A74" s="71">
         <v>46206</v>
       </c>
-      <c r="B74" s="72"/>
-      <c r="C74" s="74"/>
-      <c r="D74" s="74"/>
-      <c r="E74" s="62"/>
-      <c r="F74" s="73"/>
-      <c r="G74" s="76"/>
-      <c r="H74" s="73"/>
-      <c r="I74" s="62"/>
+      <c r="B74" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C74" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.281000990053488</v>
+      </c>
+      <c r="D74" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E74" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F74" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="G74" s="76" t="s">
+        <v>108</v>
+      </c>
+      <c r="H74" s="73" t="s">
+        <v>111</v>
+      </c>
+      <c r="I74" s="62" t="s">
+        <v>178</v>
+      </c>
       <c r="J74" s="55"/>
       <c r="K74" s="20"/>
       <c r="L74" s="20"/>
@@ -11097,16 +11318,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O74" s="18"/>
-      <c r="P74" s="18"/>
-      <c r="Q74" s="18"/>
+      <c r="O74" s="18">
+        <v>20</v>
+      </c>
+      <c r="P74" s="18">
+        <v>20</v>
+      </c>
+      <c r="Q74" s="18">
+        <v>40</v>
+      </c>
       <c r="R74" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S74" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T74" s="18">
         <f t="shared" si="46"/>
@@ -11126,19 +11353,19 @@
       </c>
       <c r="X74" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y74" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z74" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA74" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB74" s="8">
         <v>39.270000000000003</v>
@@ -11151,14 +11378,14 @@
       </c>
       <c r="AE74" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>5811.2</v>
       </c>
       <c r="AF74" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG74" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>377.72800000000001</v>
       </c>
       <c r="AH74" s="64">
         <f t="shared" si="60"/>
@@ -11166,18 +11393,18 @@
       </c>
       <c r="AI74" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>5433.4719999999998</v>
       </c>
       <c r="AJ74" s="5">
         <v>0.18</v>
       </c>
       <c r="AK74" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>978.02495999999996</v>
       </c>
       <c r="AL74" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>6411.4969599999995</v>
       </c>
       <c r="AP74" s="12"/>
     </row>
@@ -11185,15 +11412,34 @@
       <c r="A75" s="71">
         <v>46206</v>
       </c>
-      <c r="B75" s="72"/>
-      <c r="C75" s="74"/>
-      <c r="D75" s="74"/>
-      <c r="E75" s="62"/>
-      <c r="F75" s="73"/>
-      <c r="G75" s="76"/>
-      <c r="H75" s="73"/>
-      <c r="I75" s="62"/>
-      <c r="J75" s="55"/>
+      <c r="B75" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C75" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.99493668923919631</v>
+      </c>
+      <c r="D75" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E75" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F75" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="G75" s="76" t="s">
+        <v>175</v>
+      </c>
+      <c r="H75" s="73" t="s">
+        <v>111</v>
+      </c>
+      <c r="I75" s="62" t="s">
+        <v>178</v>
+      </c>
+      <c r="J75" s="55">
+        <v>40</v>
+      </c>
       <c r="K75" s="18"/>
       <c r="L75" s="18"/>
       <c r="M75" s="18"/>
@@ -11210,7 +11456,7 @@
       </c>
       <c r="S75" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T75" s="18">
         <f t="shared" si="46"/>
@@ -11255,33 +11501,33 @@
       </c>
       <c r="AE75" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF75" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG75" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH75" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI75" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ75" s="5">
         <v>0.18</v>
       </c>
       <c r="AK75" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL75" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP75" s="12"/>
     </row>
@@ -11289,21 +11535,44 @@
       <c r="A76" s="71">
         <v>46206</v>
       </c>
-      <c r="B76" s="72"/>
-      <c r="C76" s="74"/>
-      <c r="D76" s="74"/>
-      <c r="E76" s="62"/>
-      <c r="F76" s="73"/>
-      <c r="G76" s="76"/>
-      <c r="H76" s="73"/>
-      <c r="I76" s="62"/>
-      <c r="J76" s="55"/>
-      <c r="K76" s="18"/>
-      <c r="L76" s="18"/>
+      <c r="B76" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C76" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.81133216721005574</v>
+      </c>
+      <c r="D76" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E76" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F76" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="G76" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="H76" s="73" t="s">
+        <v>111</v>
+      </c>
+      <c r="I76" s="62" t="s">
+        <v>178</v>
+      </c>
+      <c r="J76" s="55">
+        <v>20</v>
+      </c>
+      <c r="K76" s="18">
+        <v>16</v>
+      </c>
+      <c r="L76" s="18">
+        <v>12</v>
+      </c>
       <c r="M76" s="18"/>
       <c r="N76" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O76" s="20"/>
       <c r="P76" s="20"/>
@@ -11314,15 +11583,15 @@
       </c>
       <c r="S76" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="T76" s="18">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U76" s="18">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V76" s="18">
         <f t="shared" si="48"/>
@@ -11330,7 +11599,7 @@
       </c>
       <c r="W76" s="8">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X76" s="18">
         <f t="shared" si="49"/>
@@ -11359,33 +11628,33 @@
       </c>
       <c r="AE76" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>5741.0700000000006</v>
       </c>
       <c r="AF76" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG76" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>373.16955000000007</v>
       </c>
       <c r="AH76" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>27.489000000000004</v>
       </c>
       <c r="AI76" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>5367.900450000001</v>
       </c>
       <c r="AJ76" s="5">
         <v>0.18</v>
       </c>
       <c r="AK76" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>966.22208100000012</v>
       </c>
       <c r="AL76" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>6334.1225310000009</v>
       </c>
       <c r="AP76" s="12"/>
     </row>
@@ -11393,21 +11662,42 @@
       <c r="A77" s="71">
         <v>46206</v>
       </c>
-      <c r="B77" s="72"/>
-      <c r="C77" s="74"/>
-      <c r="D77" s="74"/>
-      <c r="E77" s="62"/>
-      <c r="F77" s="75"/>
-      <c r="G77" s="77"/>
-      <c r="H77" s="75"/>
-      <c r="I77" s="78"/>
+      <c r="B77" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C77" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.52708988577801219</v>
+      </c>
+      <c r="D77" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E77" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F77" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="G77" s="77" t="s">
+        <v>177</v>
+      </c>
+      <c r="H77" s="73" t="s">
+        <v>111</v>
+      </c>
+      <c r="I77" s="62" t="s">
+        <v>178</v>
+      </c>
       <c r="J77" s="55"/>
-      <c r="K77" s="18"/>
-      <c r="L77" s="18"/>
+      <c r="K77" s="18">
+        <v>20</v>
+      </c>
+      <c r="L77" s="18">
+        <v>20</v>
+      </c>
       <c r="M77" s="18"/>
       <c r="N77" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O77" s="20"/>
       <c r="P77" s="20"/>
@@ -11418,15 +11708,15 @@
       </c>
       <c r="S77" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T77" s="18">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U77" s="18">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V77" s="18">
         <f t="shared" si="48"/>
@@ -11434,7 +11724,7 @@
       </c>
       <c r="W77" s="8">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X77" s="18">
         <f t="shared" si="49"/>
@@ -11463,14 +11753,14 @@
       </c>
       <c r="AE77" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>5004.1000000000004</v>
       </c>
       <c r="AF77" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG77" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>325.26650000000001</v>
       </c>
       <c r="AH77" s="64">
         <f t="shared" si="60"/>
@@ -11478,18 +11768,18 @@
       </c>
       <c r="AI77" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>4678.8335000000006</v>
       </c>
       <c r="AJ77" s="5">
         <v>0.18</v>
       </c>
       <c r="AK77" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>842.19003000000009</v>
       </c>
       <c r="AL77" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>5521.0235300000004</v>
       </c>
       <c r="AP77" s="12"/>
     </row>
@@ -11497,14 +11787,31 @@
       <c r="A78" s="71">
         <v>46206</v>
       </c>
-      <c r="B78" s="72"/>
-      <c r="C78" s="74"/>
-      <c r="D78" s="74"/>
-      <c r="E78" s="62"/>
-      <c r="F78" s="75"/>
-      <c r="G78" s="77"/>
-      <c r="H78" s="75"/>
-      <c r="I78" s="78"/>
+      <c r="B78" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C78" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.53059851968985938</v>
+      </c>
+      <c r="D78" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E78" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F78" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="G78" s="77" t="s">
+        <v>180</v>
+      </c>
+      <c r="H78" s="75" t="s">
+        <v>179</v>
+      </c>
+      <c r="I78" s="78" t="s">
+        <v>181</v>
+      </c>
       <c r="J78" s="55"/>
       <c r="K78" s="18"/>
       <c r="L78" s="18"/>
@@ -11513,16 +11820,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O78" s="20"/>
-      <c r="P78" s="20"/>
-      <c r="Q78" s="20"/>
+      <c r="O78" s="20">
+        <v>40</v>
+      </c>
+      <c r="P78" s="20">
+        <v>40</v>
+      </c>
+      <c r="Q78" s="20">
+        <v>40</v>
+      </c>
       <c r="R78" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S78" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="T78" s="18">
         <f t="shared" si="46"/>
@@ -11542,19 +11855,19 @@
       </c>
       <c r="X78" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y78" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z78" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA78" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB78" s="8">
         <v>39.270000000000003</v>
@@ -11567,14 +11880,14 @@
       </c>
       <c r="AE78" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>8716.7999999999993</v>
       </c>
       <c r="AF78" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG78" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>566.59199999999998</v>
       </c>
       <c r="AH78" s="64">
         <f t="shared" si="60"/>
@@ -11582,18 +11895,18 @@
       </c>
       <c r="AI78" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>8150.2079999999996</v>
       </c>
       <c r="AJ78" s="5">
         <v>0.18</v>
       </c>
       <c r="AK78" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1467.0374399999998</v>
       </c>
       <c r="AL78" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>9617.2454399999988</v>
       </c>
       <c r="AP78" s="12"/>
     </row>
@@ -11601,14 +11914,31 @@
       <c r="A79" s="71">
         <v>46206</v>
       </c>
-      <c r="B79" s="72"/>
-      <c r="C79" s="74"/>
-      <c r="D79" s="74"/>
-      <c r="E79" s="62"/>
-      <c r="F79" s="75"/>
-      <c r="G79" s="77"/>
-      <c r="H79" s="75"/>
-      <c r="I79" s="78"/>
+      <c r="B79" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C79" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.77966690672999484</v>
+      </c>
+      <c r="D79" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E79" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F79" s="75" t="s">
+        <v>110</v>
+      </c>
+      <c r="G79" s="77" t="s">
+        <v>182</v>
+      </c>
+      <c r="H79" s="75" t="s">
+        <v>113</v>
+      </c>
+      <c r="I79" s="78" t="s">
+        <v>189</v>
+      </c>
       <c r="J79" s="55"/>
       <c r="K79" s="18"/>
       <c r="L79" s="18"/>
@@ -11617,16 +11947,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O79" s="20"/>
-      <c r="P79" s="20"/>
-      <c r="Q79" s="20"/>
+      <c r="O79" s="20">
+        <v>10</v>
+      </c>
+      <c r="P79" s="20">
+        <v>10</v>
+      </c>
+      <c r="Q79" s="20">
+        <v>12</v>
+      </c>
       <c r="R79" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="S79" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="T79" s="18">
         <f t="shared" si="46"/>
@@ -11646,19 +11982,19 @@
       </c>
       <c r="X79" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y79" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z79" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA79" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB79" s="8">
         <v>39.270000000000003</v>
@@ -11671,14 +12007,14 @@
       </c>
       <c r="AE79" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>2324.48</v>
       </c>
       <c r="AF79" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG79" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>151.09120000000001</v>
       </c>
       <c r="AH79" s="64">
         <f t="shared" si="60"/>
@@ -11686,18 +12022,18 @@
       </c>
       <c r="AI79" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>2173.3888000000002</v>
       </c>
       <c r="AJ79" s="5">
         <v>0.18</v>
       </c>
       <c r="AK79" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>391.20998400000002</v>
       </c>
       <c r="AL79" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>2564.5987840000003</v>
       </c>
       <c r="AP79" s="12"/>
     </row>
@@ -11705,14 +12041,31 @@
       <c r="A80" s="71">
         <v>46206</v>
       </c>
-      <c r="B80" s="72"/>
-      <c r="C80" s="74"/>
-      <c r="D80" s="74"/>
-      <c r="E80" s="62"/>
-      <c r="F80" s="73"/>
-      <c r="G80" s="76"/>
-      <c r="H80" s="73"/>
-      <c r="I80" s="62"/>
+      <c r="B80" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C80" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.40968914497345255</v>
+      </c>
+      <c r="D80" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E80" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F80" s="75" t="s">
+        <v>110</v>
+      </c>
+      <c r="G80" s="76" t="s">
+        <v>183</v>
+      </c>
+      <c r="H80" s="75" t="s">
+        <v>113</v>
+      </c>
+      <c r="I80" s="78" t="s">
+        <v>189</v>
+      </c>
       <c r="J80" s="55"/>
       <c r="K80" s="20"/>
       <c r="L80" s="20"/>
@@ -11722,15 +12075,19 @@
         <v>0</v>
       </c>
       <c r="O80" s="18"/>
-      <c r="P80" s="18"/>
-      <c r="Q80" s="18"/>
+      <c r="P80" s="18">
+        <v>13</v>
+      </c>
+      <c r="Q80" s="18">
+        <v>14</v>
+      </c>
       <c r="R80" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S80" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="T80" s="18">
         <f t="shared" si="46"/>
@@ -11754,15 +12111,15 @@
       </c>
       <c r="Y80" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z80" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA80" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB80" s="8">
         <v>39.270000000000003</v>
@@ -11775,14 +12132,14 @@
       </c>
       <c r="AE80" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>1961.28</v>
       </c>
       <c r="AF80" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG80" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>127.4832</v>
       </c>
       <c r="AH80" s="64">
         <f t="shared" si="60"/>
@@ -11790,18 +12147,18 @@
       </c>
       <c r="AI80" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>1833.7968000000001</v>
       </c>
       <c r="AJ80" s="5">
         <v>0.18</v>
       </c>
       <c r="AK80" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>330.08342399999998</v>
       </c>
       <c r="AL80" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>2163.880224</v>
       </c>
       <c r="AP80" s="12"/>
     </row>
@@ -11809,21 +12166,44 @@
       <c r="A81" s="71">
         <v>46206</v>
       </c>
-      <c r="B81" s="72"/>
-      <c r="C81" s="74"/>
-      <c r="D81" s="74"/>
-      <c r="E81" s="62"/>
-      <c r="F81" s="73"/>
-      <c r="G81" s="76"/>
-      <c r="H81" s="73"/>
-      <c r="I81" s="62"/>
-      <c r="J81" s="55"/>
-      <c r="K81" s="18"/>
-      <c r="L81" s="18"/>
+      <c r="B81" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C81" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.22914538426409847</v>
+      </c>
+      <c r="D81" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E81" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F81" s="75" t="s">
+        <v>110</v>
+      </c>
+      <c r="G81" s="76" t="s">
+        <v>184</v>
+      </c>
+      <c r="H81" s="75" t="s">
+        <v>113</v>
+      </c>
+      <c r="I81" s="78" t="s">
+        <v>189</v>
+      </c>
+      <c r="J81" s="55">
+        <v>12</v>
+      </c>
+      <c r="K81" s="18">
+        <v>6</v>
+      </c>
+      <c r="L81" s="18">
+        <v>6</v>
+      </c>
       <c r="M81" s="18"/>
       <c r="N81" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O81" s="18"/>
       <c r="P81" s="18"/>
@@ -11834,15 +12214,15 @@
       </c>
       <c r="S81" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T81" s="18">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="U81" s="18">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="V81" s="18">
         <f t="shared" si="48"/>
@@ -11850,7 +12230,7 @@
       </c>
       <c r="W81" s="8">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X81" s="18">
         <f t="shared" si="49"/>
@@ -11879,33 +12259,33 @@
       </c>
       <c r="AE81" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>2844.15</v>
       </c>
       <c r="AF81" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG81" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>184.86975000000001</v>
       </c>
       <c r="AH81" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI81" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>2659.2802500000003</v>
       </c>
       <c r="AJ81" s="5">
         <v>0.18</v>
       </c>
       <c r="AK81" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>478.67044500000003</v>
       </c>
       <c r="AL81" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>3137.9506950000005</v>
       </c>
       <c r="AP81" s="12"/>
     </row>
@@ -11913,21 +12293,44 @@
       <c r="A82" s="71">
         <v>46206</v>
       </c>
-      <c r="B82" s="72"/>
-      <c r="C82" s="74"/>
-      <c r="D82" s="74"/>
-      <c r="E82" s="62"/>
-      <c r="F82" s="73"/>
-      <c r="G82" s="76"/>
-      <c r="H82" s="73"/>
-      <c r="I82" s="62"/>
-      <c r="J82" s="55"/>
-      <c r="K82" s="20"/>
-      <c r="L82" s="20"/>
+      <c r="B82" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C82" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.20069418654691784</v>
+      </c>
+      <c r="D82" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E82" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F82" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G82" s="76" t="s">
+        <v>185</v>
+      </c>
+      <c r="H82" s="75" t="s">
+        <v>113</v>
+      </c>
+      <c r="I82" s="78" t="s">
+        <v>189</v>
+      </c>
+      <c r="J82" s="55">
+        <v>6</v>
+      </c>
+      <c r="K82" s="20">
+        <v>20</v>
+      </c>
+      <c r="L82" s="20">
+        <v>20</v>
+      </c>
       <c r="M82" s="20"/>
       <c r="N82" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O82" s="18"/>
       <c r="P82" s="18"/>
@@ -11938,15 +12341,15 @@
       </c>
       <c r="S82" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="T82" s="18">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U82" s="18">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V82" s="18">
         <f t="shared" si="48"/>
@@ -11954,7 +12357,7 @@
       </c>
       <c r="W82" s="8">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X82" s="18">
         <f t="shared" si="49"/>
@@ -11983,33 +12386,33 @@
       </c>
       <c r="AE82" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>5675.5599999999995</v>
       </c>
       <c r="AF82" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG82" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>368.91139999999996</v>
       </c>
       <c r="AH82" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>8.2467000000000006</v>
       </c>
       <c r="AI82" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>5306.6485999999995</v>
       </c>
       <c r="AJ82" s="5">
         <v>0.18</v>
       </c>
       <c r="AK82" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>955.19674799999984</v>
       </c>
       <c r="AL82" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>6261.8453479999989</v>
       </c>
       <c r="AP82" s="12"/>
     </row>
@@ -12017,15 +12420,34 @@
       <c r="A83" s="71">
         <v>46206</v>
       </c>
-      <c r="B83" s="72"/>
-      <c r="C83" s="74"/>
-      <c r="D83" s="74"/>
-      <c r="E83" s="62"/>
-      <c r="F83" s="73"/>
-      <c r="G83" s="76"/>
-      <c r="H83" s="73"/>
-      <c r="I83" s="62"/>
-      <c r="J83" s="55"/>
+      <c r="B83" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C83" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.57624247604564405</v>
+      </c>
+      <c r="D83" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E83" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F83" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G83" s="76" t="s">
+        <v>186</v>
+      </c>
+      <c r="H83" s="75" t="s">
+        <v>113</v>
+      </c>
+      <c r="I83" s="78" t="s">
+        <v>189</v>
+      </c>
+      <c r="J83" s="55">
+        <v>12</v>
+      </c>
       <c r="K83" s="20"/>
       <c r="L83" s="20"/>
       <c r="M83" s="20"/>
@@ -12042,7 +12464,7 @@
       </c>
       <c r="S83" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T83" s="18">
         <f t="shared" si="46"/>
@@ -12087,33 +12509,33 @@
       </c>
       <c r="AE83" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>1342.92</v>
       </c>
       <c r="AF83" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG83" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>87.289800000000014</v>
       </c>
       <c r="AH83" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI83" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>1255.6302000000001</v>
       </c>
       <c r="AJ83" s="5">
         <v>0.18</v>
       </c>
       <c r="AK83" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>226.01343600000001</v>
       </c>
       <c r="AL83" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>1481.643636</v>
       </c>
       <c r="AP83" s="12"/>
     </row>
@@ -12121,15 +12543,34 @@
       <c r="A84" s="71">
         <v>46206</v>
       </c>
-      <c r="B84" s="72"/>
-      <c r="C84" s="74"/>
-      <c r="D84" s="74"/>
-      <c r="E84" s="62"/>
-      <c r="F84" s="73"/>
-      <c r="G84" s="76"/>
-      <c r="H84" s="73"/>
-      <c r="I84" s="62"/>
-      <c r="J84" s="55"/>
+      <c r="B84" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C84" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.29185613204431193</v>
+      </c>
+      <c r="D84" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E84" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F84" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G84" s="76" t="s">
+        <v>187</v>
+      </c>
+      <c r="H84" s="75" t="s">
+        <v>113</v>
+      </c>
+      <c r="I84" s="78" t="s">
+        <v>189</v>
+      </c>
+      <c r="J84" s="55">
+        <v>10</v>
+      </c>
       <c r="K84" s="20"/>
       <c r="L84" s="20"/>
       <c r="M84" s="20"/>
@@ -12137,16 +12578,20 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O84" s="20"/>
+      <c r="O84" s="20">
+        <v>6</v>
+      </c>
       <c r="P84" s="18"/>
-      <c r="Q84" s="18"/>
+      <c r="Q84" s="18">
+        <v>6</v>
+      </c>
       <c r="R84" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S84" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T84" s="18">
         <f t="shared" si="46"/>
@@ -12166,7 +12611,7 @@
       </c>
       <c r="X84" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Y84" s="18">
         <f t="shared" si="50"/>
@@ -12174,11 +12619,11 @@
       </c>
       <c r="Z84" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AA84" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB84" s="8">
         <v>39.270000000000003</v>
@@ -12191,33 +12636,33 @@
       </c>
       <c r="AE84" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>1990.78</v>
       </c>
       <c r="AF84" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG84" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>129.4007</v>
       </c>
       <c r="AH84" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI84" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>1861.3793000000001</v>
       </c>
       <c r="AJ84" s="5">
         <v>0.18</v>
       </c>
       <c r="AK84" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>335.04827399999999</v>
       </c>
       <c r="AL84" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>2196.4275740000003</v>
       </c>
       <c r="AP84" s="12"/>
     </row>
@@ -12225,14 +12670,31 @@
       <c r="A85" s="71">
         <v>46206</v>
       </c>
-      <c r="B85" s="72"/>
-      <c r="C85" s="74"/>
-      <c r="D85" s="74"/>
-      <c r="E85" s="62"/>
-      <c r="F85" s="73"/>
-      <c r="G85" s="76"/>
-      <c r="H85" s="73"/>
-      <c r="I85" s="62"/>
+      <c r="B85" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C85" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.42552384863610082</v>
+      </c>
+      <c r="D85" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E85" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F85" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G85" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="H85" s="75" t="s">
+        <v>113</v>
+      </c>
+      <c r="I85" s="78" t="s">
+        <v>189</v>
+      </c>
       <c r="J85" s="55"/>
       <c r="K85" s="20"/>
       <c r="L85" s="20"/>
@@ -12241,16 +12703,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O85" s="18"/>
-      <c r="P85" s="20"/>
-      <c r="Q85" s="20"/>
+      <c r="O85" s="18">
+        <v>13</v>
+      </c>
+      <c r="P85" s="20">
+        <v>13</v>
+      </c>
+      <c r="Q85" s="20">
+        <v>14</v>
+      </c>
       <c r="R85" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S85" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T85" s="18">
         <f t="shared" si="46"/>
@@ -12270,19 +12738,19 @@
       </c>
       <c r="X85" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Y85" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z85" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA85" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB85" s="8">
         <v>39.270000000000003</v>
@@ -12295,14 +12763,14 @@
       </c>
       <c r="AE85" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF85" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG85" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH85" s="64">
         <f t="shared" si="60"/>
@@ -12310,18 +12778,18 @@
       </c>
       <c r="AI85" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ85" s="5">
         <v>0.18</v>
       </c>
       <c r="AK85" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL85" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP85" s="12"/>
     </row>
@@ -12329,15 +12797,34 @@
       <c r="A86" s="71">
         <v>46206</v>
       </c>
-      <c r="B86" s="72"/>
-      <c r="C86" s="74"/>
-      <c r="D86" s="74"/>
-      <c r="E86" s="62"/>
-      <c r="F86" s="73"/>
-      <c r="G86" s="76"/>
-      <c r="H86" s="73"/>
-      <c r="I86" s="62"/>
-      <c r="J86" s="55"/>
+      <c r="B86" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C86" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.79099252348512739</v>
+      </c>
+      <c r="D86" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E86" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F86" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="G86" s="76" t="s">
+        <v>190</v>
+      </c>
+      <c r="H86" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="I86" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="J86" s="55">
+        <v>40</v>
+      </c>
       <c r="K86" s="18"/>
       <c r="L86" s="18"/>
       <c r="M86" s="18"/>
@@ -12345,16 +12832,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O86" s="18"/>
-      <c r="P86" s="18"/>
-      <c r="Q86" s="18"/>
+      <c r="O86" s="18">
+        <v>15</v>
+      </c>
+      <c r="P86" s="18">
+        <v>15</v>
+      </c>
+      <c r="Q86" s="18">
+        <v>10</v>
+      </c>
       <c r="R86" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S86" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T86" s="18">
         <f t="shared" si="46"/>
@@ -12374,19 +12867,19 @@
       </c>
       <c r="X86" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y86" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z86" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA86" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB86" s="8">
         <v>39.270000000000003</v>
@@ -12399,33 +12892,33 @@
       </c>
       <c r="AE86" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>7382</v>
       </c>
       <c r="AF86" s="21">
         <v>0.14000000000000001</v>
       </c>
       <c r="AG86" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>1033.48</v>
       </c>
       <c r="AH86" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI86" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>6348.52</v>
       </c>
       <c r="AJ86" s="5">
         <v>0.18</v>
       </c>
       <c r="AK86" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1142.7336</v>
       </c>
       <c r="AL86" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>7491.2536</v>
       </c>
       <c r="AP86" s="12"/>
     </row>
@@ -12433,15 +12926,34 @@
       <c r="A87" s="71">
         <v>46206</v>
       </c>
-      <c r="B87" s="72"/>
-      <c r="C87" s="74"/>
-      <c r="D87" s="74"/>
-      <c r="E87" s="62"/>
-      <c r="F87" s="73"/>
-      <c r="G87" s="76"/>
-      <c r="H87" s="73"/>
-      <c r="I87" s="62"/>
-      <c r="J87" s="55"/>
+      <c r="B87" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C87" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.59567178391915743</v>
+      </c>
+      <c r="D87" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E87" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F87" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G87" s="76" t="s">
+        <v>191</v>
+      </c>
+      <c r="H87" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="I87" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="J87" s="55">
+        <v>12</v>
+      </c>
       <c r="K87" s="18"/>
       <c r="L87" s="18"/>
       <c r="M87" s="18"/>
@@ -12458,7 +12970,7 @@
       </c>
       <c r="S87" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T87" s="18">
         <f t="shared" si="46"/>
@@ -12503,33 +13015,33 @@
       </c>
       <c r="AE87" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>1342.92</v>
       </c>
       <c r="AF87" s="21">
         <v>0.14000000000000001</v>
       </c>
       <c r="AG87" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>188.00880000000004</v>
       </c>
       <c r="AH87" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI87" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>1154.9112</v>
       </c>
       <c r="AJ87" s="5">
         <v>0.18</v>
       </c>
       <c r="AK87" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>207.884016</v>
       </c>
       <c r="AL87" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>1362.795216</v>
       </c>
       <c r="AP87" s="12"/>
     </row>
@@ -12537,40 +13049,69 @@
       <c r="A88" s="71">
         <v>46206</v>
       </c>
-      <c r="B88" s="72"/>
-      <c r="C88" s="74"/>
-      <c r="D88" s="74"/>
-      <c r="E88" s="62"/>
-      <c r="F88" s="73"/>
-      <c r="G88" s="76"/>
-      <c r="H88" s="73"/>
-      <c r="I88" s="62"/>
-      <c r="J88" s="55"/>
-      <c r="K88" s="18"/>
-      <c r="L88" s="18"/>
+      <c r="B88" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C88" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.59249319913705234</v>
+      </c>
+      <c r="D88" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E88" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F88" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G88" s="76" t="s">
+        <v>162</v>
+      </c>
+      <c r="H88" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="I88" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="J88" s="55">
+        <v>40</v>
+      </c>
+      <c r="K88" s="18">
+        <v>20</v>
+      </c>
+      <c r="L88" s="18">
+        <v>20</v>
+      </c>
       <c r="M88" s="18"/>
       <c r="N88" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="O88" s="20"/>
-      <c r="P88" s="20"/>
-      <c r="Q88" s="20"/>
+        <v>40</v>
+      </c>
+      <c r="O88" s="20">
+        <v>40</v>
+      </c>
+      <c r="P88" s="20">
+        <v>40</v>
+      </c>
+      <c r="Q88" s="20">
+        <v>40</v>
+      </c>
       <c r="R88" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S88" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T88" s="18">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U88" s="18">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V88" s="18">
         <f t="shared" si="48"/>
@@ -12578,23 +13119,23 @@
       </c>
       <c r="W88" s="8">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X88" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y88" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z88" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA88" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB88" s="8">
         <v>39.270000000000003</v>
@@ -12607,47 +13148,68 @@
       </c>
       <c r="AE88" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>18197.3</v>
       </c>
       <c r="AF88" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG88" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>1182.8244999999999</v>
       </c>
       <c r="AH88" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI88" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>17014.4755</v>
       </c>
       <c r="AJ88" s="5">
         <v>0.18</v>
       </c>
       <c r="AK88" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>3062.6055900000001</v>
       </c>
       <c r="AL88" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>20077.08109</v>
       </c>
       <c r="AP88" s="12"/>
     </row>
     <row r="89" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A89" s="71"/>
-      <c r="B89" s="72"/>
-      <c r="C89" s="74"/>
-      <c r="D89" s="74"/>
-      <c r="E89" s="62"/>
-      <c r="F89" s="73"/>
-      <c r="G89" s="76"/>
-      <c r="H89" s="73"/>
-      <c r="I89" s="62"/>
-      <c r="J89" s="55"/>
+      <c r="A89" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B89" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C89" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.34619066216321537</v>
+      </c>
+      <c r="D89" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E89" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F89" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="G89" s="76" t="s">
+        <v>192</v>
+      </c>
+      <c r="H89" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="I89" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="J89" s="55">
+        <v>40</v>
+      </c>
       <c r="K89" s="20"/>
       <c r="L89" s="20"/>
       <c r="M89" s="20"/>
@@ -12655,16 +13217,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O89" s="18"/>
-      <c r="P89" s="18"/>
-      <c r="Q89" s="18"/>
+      <c r="O89" s="18">
+        <v>10</v>
+      </c>
+      <c r="P89" s="18">
+        <v>10</v>
+      </c>
+      <c r="Q89" s="18">
+        <v>20</v>
+      </c>
       <c r="R89" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S89" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T89" s="18">
         <f t="shared" si="46"/>
@@ -12684,19 +13252,19 @@
       </c>
       <c r="X89" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y89" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z89" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA89" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB89" s="8">
         <v>39.270000000000003</v>
@@ -12709,47 +13277,68 @@
       </c>
       <c r="AE89" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>7382</v>
       </c>
       <c r="AF89" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG89" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>479.83000000000004</v>
       </c>
       <c r="AH89" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI89" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>6902.17</v>
       </c>
       <c r="AJ89" s="5">
         <v>0.18</v>
       </c>
       <c r="AK89" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1242.3905999999999</v>
       </c>
       <c r="AL89" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>8144.5605999999998</v>
       </c>
       <c r="AP89" s="12"/>
     </row>
     <row r="90" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A90" s="71"/>
-      <c r="B90" s="72"/>
-      <c r="C90" s="74"/>
-      <c r="D90" s="74"/>
-      <c r="E90" s="62"/>
-      <c r="F90" s="73"/>
-      <c r="G90" s="76"/>
-      <c r="H90" s="73"/>
-      <c r="I90" s="62"/>
-      <c r="J90" s="55"/>
+      <c r="A90" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B90" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C90" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.7542120362532948</v>
+      </c>
+      <c r="D90" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E90" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F90" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G90" s="76" t="s">
+        <v>193</v>
+      </c>
+      <c r="H90" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="I90" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="J90" s="55">
+        <v>400</v>
+      </c>
       <c r="K90" s="18"/>
       <c r="L90" s="18"/>
       <c r="M90" s="18"/>
@@ -12757,16 +13346,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O90" s="20"/>
-      <c r="P90" s="20"/>
-      <c r="Q90" s="20"/>
+      <c r="O90" s="20">
+        <v>80</v>
+      </c>
+      <c r="P90" s="20">
+        <v>80</v>
+      </c>
+      <c r="Q90" s="20">
+        <v>40</v>
+      </c>
       <c r="R90" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S90" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="T90" s="18">
         <f t="shared" si="46"/>
@@ -12786,19 +13381,19 @@
       </c>
       <c r="X90" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y90" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z90" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA90" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AB90" s="8">
         <v>39.270000000000003</v>
@@ -12811,47 +13406,68 @@
       </c>
       <c r="AE90" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>59292</v>
       </c>
       <c r="AF90" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG90" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>3853.98</v>
       </c>
       <c r="AH90" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>549.78000000000009</v>
       </c>
       <c r="AI90" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>55438.02</v>
       </c>
       <c r="AJ90" s="5">
         <v>0.18</v>
       </c>
       <c r="AK90" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>9978.8435999999983</v>
       </c>
       <c r="AL90" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>65416.863599999997</v>
       </c>
       <c r="AP90" s="12"/>
     </row>
     <row r="91" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A91" s="71"/>
-      <c r="B91" s="72"/>
-      <c r="C91" s="74"/>
-      <c r="D91" s="74"/>
-      <c r="E91" s="62"/>
-      <c r="F91" s="73"/>
-      <c r="G91" s="76"/>
-      <c r="H91" s="73"/>
-      <c r="I91" s="62"/>
-      <c r="J91" s="55"/>
+      <c r="A91" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B91" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C91" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.82410056877402549</v>
+      </c>
+      <c r="D91" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E91" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F91" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="G91" s="76" t="s">
+        <v>194</v>
+      </c>
+      <c r="H91" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="I91" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="J91" s="55">
+        <v>40</v>
+      </c>
       <c r="K91" s="18"/>
       <c r="L91" s="20"/>
       <c r="M91" s="20"/>
@@ -12868,7 +13484,7 @@
       </c>
       <c r="S91" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T91" s="18">
         <f t="shared" si="46"/>
@@ -12913,53 +13529,76 @@
       </c>
       <c r="AE91" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF91" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG91" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH91" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI91" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ91" s="5">
         <v>0.18</v>
       </c>
       <c r="AK91" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL91" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP91" s="12"/>
     </row>
     <row r="92" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A92" s="71"/>
-      <c r="B92" s="72"/>
-      <c r="C92" s="74"/>
-      <c r="D92" s="74"/>
-      <c r="E92" s="62"/>
-      <c r="F92" s="75"/>
-      <c r="G92" s="77"/>
-      <c r="H92" s="75"/>
-      <c r="I92" s="78"/>
-      <c r="J92" s="55"/>
-      <c r="K92" s="69"/>
+      <c r="A92" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B92" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C92" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.96351266436405625</v>
+      </c>
+      <c r="D92" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E92" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F92" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="G92" s="77" t="s">
+        <v>196</v>
+      </c>
+      <c r="H92" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="I92" s="78" t="s">
+        <v>202</v>
+      </c>
+      <c r="J92" s="55">
+        <v>10</v>
+      </c>
+      <c r="K92" s="69">
+        <v>10</v>
+      </c>
       <c r="L92" s="70"/>
       <c r="M92" s="70"/>
       <c r="N92" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O92" s="69"/>
       <c r="P92" s="70"/>
@@ -12970,11 +13609,11 @@
       </c>
       <c r="S92" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T92" s="18">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U92" s="18">
         <f t="shared" si="47"/>
@@ -12986,7 +13625,7 @@
       </c>
       <c r="W92" s="8">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X92" s="18">
         <f t="shared" si="49"/>
@@ -13015,46 +13654,65 @@
       </c>
       <c r="AE92" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>2370.125</v>
       </c>
       <c r="AF92" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG92" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>154.05812500000002</v>
       </c>
       <c r="AH92" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI92" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>2216.066875</v>
       </c>
       <c r="AJ92" s="5">
         <v>0.18</v>
       </c>
       <c r="AK92" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>398.89203749999996</v>
       </c>
       <c r="AL92" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>2614.9589124999998</v>
       </c>
       <c r="AP92" s="12"/>
     </row>
     <row r="93" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
-      <c r="B93" s="72"/>
-      <c r="C93" s="74"/>
-      <c r="D93" s="74"/>
-      <c r="E93" s="62"/>
-      <c r="F93" s="75"/>
-      <c r="G93" s="77"/>
-      <c r="H93" s="75"/>
-      <c r="I93" s="78"/>
+      <c r="A93" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B93" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C93" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.45253581790315889</v>
+      </c>
+      <c r="D93" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E93" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F93" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="G93" s="77" t="s">
+        <v>142</v>
+      </c>
+      <c r="H93" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="I93" s="78" t="s">
+        <v>202</v>
+      </c>
       <c r="J93" s="55"/>
       <c r="K93" s="69"/>
       <c r="L93" s="70"/>
@@ -13065,14 +13723,16 @@
       </c>
       <c r="O93" s="69"/>
       <c r="P93" s="70"/>
-      <c r="Q93" s="70"/>
+      <c r="Q93" s="70">
+        <v>10</v>
+      </c>
       <c r="R93" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S93" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T93" s="18">
         <f t="shared" si="46"/>
@@ -13100,11 +13760,11 @@
       </c>
       <c r="Z93" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA93" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB93" s="8">
         <v>39.270000000000003</v>
@@ -13117,14 +13777,14 @@
       </c>
       <c r="AE93" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>726.4</v>
       </c>
       <c r="AF93" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG93" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>47.216000000000001</v>
       </c>
       <c r="AH93" s="64">
         <f t="shared" si="60"/>
@@ -13132,31 +13792,50 @@
       </c>
       <c r="AI93" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>679.18399999999997</v>
       </c>
       <c r="AJ93" s="5">
         <v>0.18</v>
       </c>
       <c r="AK93" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>122.25312</v>
       </c>
       <c r="AL93" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>801.43711999999994</v>
       </c>
       <c r="AP93" s="12"/>
     </row>
     <row r="94" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
-      <c r="B94" s="72"/>
-      <c r="C94" s="74"/>
-      <c r="D94" s="74"/>
-      <c r="E94" s="62"/>
-      <c r="F94" s="75"/>
-      <c r="G94" s="77"/>
-      <c r="H94" s="75"/>
-      <c r="I94" s="78"/>
+      <c r="A94" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B94" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C94" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.54179084432051094</v>
+      </c>
+      <c r="D94" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E94" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F94" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="G94" s="77" t="s">
+        <v>142</v>
+      </c>
+      <c r="H94" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="I94" s="78" t="s">
+        <v>202</v>
+      </c>
       <c r="J94" s="55"/>
       <c r="K94" s="69"/>
       <c r="L94" s="70"/>
@@ -13167,14 +13846,16 @@
       </c>
       <c r="O94" s="69"/>
       <c r="P94" s="70"/>
-      <c r="Q94" s="70"/>
+      <c r="Q94" s="70">
+        <v>10</v>
+      </c>
       <c r="R94" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S94" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T94" s="18">
         <f t="shared" si="46"/>
@@ -13202,11 +13883,11 @@
       </c>
       <c r="Z94" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA94" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB94" s="8">
         <v>39.270000000000003</v>
@@ -13219,14 +13900,14 @@
       </c>
       <c r="AE94" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>726.4</v>
       </c>
       <c r="AF94" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG94" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>47.216000000000001</v>
       </c>
       <c r="AH94" s="64">
         <f t="shared" si="60"/>
@@ -13234,32 +13915,53 @@
       </c>
       <c r="AI94" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>679.18399999999997</v>
       </c>
       <c r="AJ94" s="5">
         <v>0.18</v>
       </c>
       <c r="AK94" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>122.25312</v>
       </c>
       <c r="AL94" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>801.43711999999994</v>
       </c>
       <c r="AP94" s="12"/>
     </row>
     <row r="95" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
-      <c r="B95" s="72"/>
-      <c r="C95" s="74"/>
-      <c r="D95" s="74"/>
-      <c r="E95" s="62"/>
-      <c r="F95" s="75"/>
-      <c r="G95" s="77"/>
-      <c r="H95" s="75"/>
-      <c r="I95" s="78"/>
-      <c r="J95" s="55"/>
+      <c r="A95" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B95" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C95" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.11793538317589858</v>
+      </c>
+      <c r="D95" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E95" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F95" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="G95" s="77" t="s">
+        <v>197</v>
+      </c>
+      <c r="H95" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="I95" s="78" t="s">
+        <v>202</v>
+      </c>
+      <c r="J95" s="55">
+        <v>80</v>
+      </c>
       <c r="K95" s="69"/>
       <c r="L95" s="70"/>
       <c r="M95" s="70"/>
@@ -13268,15 +13970,19 @@
         <v>0</v>
       </c>
       <c r="O95" s="69"/>
-      <c r="P95" s="70"/>
-      <c r="Q95" s="70"/>
+      <c r="P95" s="70">
+        <v>40</v>
+      </c>
+      <c r="Q95" s="70">
+        <v>80</v>
+      </c>
       <c r="R95" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S95" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T95" s="18">
         <f t="shared" si="46"/>
@@ -13300,15 +14006,15 @@
       </c>
       <c r="Y95" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z95" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA95" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB95" s="8">
         <v>39.270000000000003</v>
@@ -13321,72 +14027,103 @@
       </c>
       <c r="AE95" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>17669.599999999999</v>
       </c>
       <c r="AF95" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG95" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>1148.5239999999999</v>
       </c>
       <c r="AH95" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>109.95600000000002</v>
       </c>
       <c r="AI95" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>16521.075999999997</v>
       </c>
       <c r="AJ95" s="5">
         <v>0.18</v>
       </c>
       <c r="AK95" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>2973.7936799999993</v>
       </c>
       <c r="AL95" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>19494.869679999996</v>
       </c>
       <c r="AP95" s="12"/>
     </row>
     <row r="96" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
-      <c r="B96" s="72"/>
-      <c r="C96" s="74"/>
-      <c r="D96" s="74"/>
-      <c r="E96" s="62"/>
-      <c r="F96" s="73"/>
-      <c r="G96" s="76"/>
-      <c r="H96" s="73"/>
-      <c r="I96" s="62"/>
-      <c r="J96" s="55"/>
-      <c r="K96" s="20"/>
-      <c r="L96" s="20"/>
+      <c r="A96" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B96" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C96" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>7.6368324223456074E-2</v>
+      </c>
+      <c r="D96" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E96" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F96" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="G96" s="76" t="s">
+        <v>198</v>
+      </c>
+      <c r="H96" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="I96" s="78" t="s">
+        <v>202</v>
+      </c>
+      <c r="J96" s="55">
+        <v>10</v>
+      </c>
+      <c r="K96" s="20">
+        <v>10</v>
+      </c>
+      <c r="L96" s="20">
+        <v>10</v>
+      </c>
       <c r="M96" s="18"/>
       <c r="N96" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="O96" s="20"/>
-      <c r="P96" s="18"/>
-      <c r="Q96" s="20"/>
+        <v>20</v>
+      </c>
+      <c r="O96" s="20">
+        <v>20</v>
+      </c>
+      <c r="P96" s="18">
+        <v>10</v>
+      </c>
+      <c r="Q96" s="20">
+        <v>10</v>
+      </c>
       <c r="R96" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S96" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="T96" s="18">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U96" s="18">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V96" s="18">
         <f t="shared" si="48"/>
@@ -13394,23 +14131,23 @@
       </c>
       <c r="W96" s="8">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X96" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y96" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z96" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA96" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB96" s="8">
         <v>39.270000000000003</v>
@@ -13423,64 +14160,89 @@
       </c>
       <c r="AE96" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>6526.75</v>
       </c>
       <c r="AF96" s="21">
         <v>0.1</v>
       </c>
       <c r="AG96" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>652.67500000000007</v>
       </c>
       <c r="AH96" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI96" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>5874.0749999999998</v>
       </c>
       <c r="AJ96" s="5">
         <v>0.18</v>
       </c>
       <c r="AK96" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1057.3335</v>
       </c>
       <c r="AL96" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>6931.4084999999995</v>
       </c>
       <c r="AP96" s="12"/>
     </row>
     <row r="97" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A97" s="71"/>
-      <c r="B97" s="72"/>
-      <c r="C97" s="74"/>
-      <c r="D97" s="74"/>
-      <c r="E97" s="62"/>
-      <c r="F97" s="73"/>
-      <c r="G97" s="76"/>
-      <c r="H97" s="73"/>
-      <c r="I97" s="62"/>
+      <c r="A97" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B97" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C97" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.71299769211550057</v>
+      </c>
+      <c r="D97" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E97" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F97" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G97" s="76" t="s">
+        <v>199</v>
+      </c>
+      <c r="H97" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="I97" s="78" t="s">
+        <v>202</v>
+      </c>
       <c r="J97" s="55"/>
       <c r="K97" s="18"/>
-      <c r="L97" s="18"/>
+      <c r="L97" s="18">
+        <v>20</v>
+      </c>
       <c r="M97" s="18"/>
       <c r="N97" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="O97" s="20"/>
+        <v>20</v>
+      </c>
+      <c r="O97" s="20">
+        <v>10</v>
+      </c>
       <c r="P97" s="20"/>
-      <c r="Q97" s="20"/>
+      <c r="Q97" s="20">
+        <v>10</v>
+      </c>
       <c r="R97" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S97" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T97" s="18">
         <f t="shared" si="46"/>
@@ -13488,7 +14250,7 @@
       </c>
       <c r="U97" s="18">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V97" s="18">
         <f t="shared" si="48"/>
@@ -13496,11 +14258,11 @@
       </c>
       <c r="W97" s="8">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X97" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y97" s="18">
         <f t="shared" si="50"/>
@@ -13508,11 +14270,11 @@
       </c>
       <c r="Z97" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA97" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB97" s="8">
         <v>39.270000000000003</v>
@@ -13525,14 +14287,14 @@
       </c>
       <c r="AE97" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>3954.85</v>
       </c>
       <c r="AF97" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG97" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>257.06524999999999</v>
       </c>
       <c r="AH97" s="64">
         <f t="shared" si="60"/>
@@ -13540,31 +14302,50 @@
       </c>
       <c r="AI97" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>3697.7847499999998</v>
       </c>
       <c r="AJ97" s="5">
         <v>0.18</v>
       </c>
       <c r="AK97" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>665.60125499999992</v>
       </c>
       <c r="AL97" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>4363.3860049999994</v>
       </c>
       <c r="AP97" s="12"/>
     </row>
     <row r="98" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A98" s="71"/>
-      <c r="B98" s="72"/>
-      <c r="C98" s="74"/>
-      <c r="D98" s="74"/>
-      <c r="E98" s="62"/>
-      <c r="F98" s="73"/>
-      <c r="G98" s="76"/>
-      <c r="H98" s="73"/>
-      <c r="I98" s="62"/>
+      <c r="A98" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B98" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C98" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.90303964520365554</v>
+      </c>
+      <c r="D98" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E98" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F98" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="G98" s="76" t="s">
+        <v>200</v>
+      </c>
+      <c r="H98" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="I98" s="78" t="s">
+        <v>202</v>
+      </c>
       <c r="J98" s="55"/>
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
@@ -13575,14 +14356,16 @@
       </c>
       <c r="O98" s="18"/>
       <c r="P98" s="18"/>
-      <c r="Q98" s="18"/>
+      <c r="Q98" s="18">
+        <v>10</v>
+      </c>
       <c r="R98" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S98" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T98" s="18">
         <f t="shared" si="46"/>
@@ -13610,11 +14393,11 @@
       </c>
       <c r="Z98" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA98" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB98" s="8">
         <v>39.270000000000003</v>
@@ -13627,14 +14410,14 @@
       </c>
       <c r="AE98" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>726.4</v>
       </c>
       <c r="AF98" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG98" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>47.216000000000001</v>
       </c>
       <c r="AH98" s="64">
         <f t="shared" si="60"/>
@@ -13642,31 +14425,50 @@
       </c>
       <c r="AI98" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>679.18399999999997</v>
       </c>
       <c r="AJ98" s="5">
         <v>0.18</v>
       </c>
       <c r="AK98" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>122.25312</v>
       </c>
       <c r="AL98" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>801.43711999999994</v>
       </c>
       <c r="AP98" s="12"/>
     </row>
     <row r="99" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A99" s="71"/>
-      <c r="B99" s="72"/>
-      <c r="C99" s="74"/>
-      <c r="D99" s="74"/>
-      <c r="E99" s="62"/>
-      <c r="F99" s="73"/>
-      <c r="G99" s="76"/>
-      <c r="H99" s="73"/>
-      <c r="I99" s="62"/>
+      <c r="A99" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B99" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C99" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.63454196761225568</v>
+      </c>
+      <c r="D99" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E99" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F99" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="G99" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="H99" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="I99" s="78" t="s">
+        <v>202</v>
+      </c>
       <c r="J99" s="55"/>
       <c r="K99" s="18"/>
       <c r="L99" s="18"/>
@@ -13677,14 +14479,16 @@
       </c>
       <c r="O99" s="20"/>
       <c r="P99" s="20"/>
-      <c r="Q99" s="20"/>
+      <c r="Q99" s="20">
+        <v>10</v>
+      </c>
       <c r="R99" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S99" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T99" s="18">
         <f t="shared" si="46"/>
@@ -13712,11 +14516,11 @@
       </c>
       <c r="Z99" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA99" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB99" s="8">
         <v>39.270000000000003</v>
@@ -13729,14 +14533,14 @@
       </c>
       <c r="AE99" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>726.4</v>
       </c>
       <c r="AF99" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG99" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>47.216000000000001</v>
       </c>
       <c r="AH99" s="64">
         <f t="shared" si="60"/>
@@ -13744,31 +14548,50 @@
       </c>
       <c r="AI99" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>679.18399999999997</v>
       </c>
       <c r="AJ99" s="5">
         <v>0.18</v>
       </c>
       <c r="AK99" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>122.25312</v>
       </c>
       <c r="AL99" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>801.43711999999994</v>
       </c>
       <c r="AP99" s="12"/>
     </row>
     <row r="100" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A100" s="71"/>
-      <c r="B100" s="72"/>
-      <c r="C100" s="74"/>
-      <c r="D100" s="74"/>
-      <c r="E100" s="62"/>
-      <c r="F100" s="73"/>
-      <c r="G100" s="76"/>
-      <c r="H100" s="73"/>
-      <c r="I100" s="62"/>
+      <c r="A100" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B100" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C100" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.89620235247076585</v>
+      </c>
+      <c r="D100" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E100" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F100" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G100" s="76" t="s">
+        <v>145</v>
+      </c>
+      <c r="H100" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="I100" s="78" t="s">
+        <v>202</v>
+      </c>
       <c r="J100" s="55"/>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -13777,16 +14600,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O100" s="18"/>
-      <c r="P100" s="18"/>
-      <c r="Q100" s="18"/>
+      <c r="O100" s="18">
+        <v>15</v>
+      </c>
+      <c r="P100" s="18">
+        <v>10</v>
+      </c>
+      <c r="Q100" s="18">
+        <v>15</v>
+      </c>
       <c r="R100" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S100" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T100" s="18">
         <f t="shared" si="46"/>
@@ -13806,19 +14635,19 @@
       </c>
       <c r="X100" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y100" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z100" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA100" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB100" s="8">
         <v>39.270000000000003</v>
@@ -13831,14 +14660,14 @@
       </c>
       <c r="AE100" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF100" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG100" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH100" s="64">
         <f t="shared" si="60"/>
@@ -13846,31 +14675,50 @@
       </c>
       <c r="AI100" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ100" s="5">
         <v>0.18</v>
       </c>
       <c r="AK100" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL100" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP100" s="12"/>
     </row>
     <row r="101" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A101" s="71"/>
-      <c r="B101" s="72"/>
-      <c r="C101" s="74"/>
-      <c r="D101" s="74"/>
-      <c r="E101" s="62"/>
-      <c r="F101" s="73"/>
-      <c r="G101" s="76"/>
-      <c r="H101" s="73"/>
-      <c r="I101" s="62"/>
+      <c r="A101" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B101" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C101" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.41879354157924686</v>
+      </c>
+      <c r="D101" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E101" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F101" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G101" s="76" t="s">
+        <v>203</v>
+      </c>
+      <c r="H101" s="73" t="s">
+        <v>179</v>
+      </c>
+      <c r="I101" s="62" t="s">
+        <v>211</v>
+      </c>
       <c r="J101" s="55"/>
       <c r="K101" s="18"/>
       <c r="L101" s="20"/>
@@ -13879,16 +14727,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O101" s="20"/>
-      <c r="P101" s="20"/>
-      <c r="Q101" s="20"/>
+      <c r="O101" s="20">
+        <v>40</v>
+      </c>
+      <c r="P101" s="20">
+        <v>40</v>
+      </c>
+      <c r="Q101" s="20">
+        <v>80</v>
+      </c>
       <c r="R101" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="S101" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="T101" s="18">
         <f t="shared" si="46"/>
@@ -13908,19 +14762,19 @@
       </c>
       <c r="X101" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y101" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z101" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA101" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AB101" s="8">
         <v>39.270000000000003</v>
@@ -13933,14 +14787,14 @@
       </c>
       <c r="AE101" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>11622.4</v>
       </c>
       <c r="AF101" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG101" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>755.45600000000002</v>
       </c>
       <c r="AH101" s="64">
         <f t="shared" si="60"/>
@@ -13948,31 +14802,50 @@
       </c>
       <c r="AI101" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>10866.944</v>
       </c>
       <c r="AJ101" s="5">
         <v>0.18</v>
       </c>
       <c r="AK101" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1956.0499199999999</v>
       </c>
       <c r="AL101" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>12822.993919999999</v>
       </c>
       <c r="AP101" s="12"/>
     </row>
     <row r="102" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A102" s="71"/>
-      <c r="B102" s="72"/>
-      <c r="C102" s="74"/>
-      <c r="D102" s="74"/>
-      <c r="E102" s="62"/>
-      <c r="F102" s="73"/>
-      <c r="G102" s="76"/>
-      <c r="H102" s="73"/>
-      <c r="I102" s="62"/>
+      <c r="A102" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B102" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C102" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.12463213379403992</v>
+      </c>
+      <c r="D102" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E102" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F102" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G102" s="76" t="s">
+        <v>204</v>
+      </c>
+      <c r="H102" s="73" t="s">
+        <v>179</v>
+      </c>
+      <c r="I102" s="62" t="s">
+        <v>211</v>
+      </c>
       <c r="J102" s="55"/>
       <c r="K102" s="18"/>
       <c r="L102" s="18"/>
@@ -13981,16 +14854,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O102" s="20"/>
-      <c r="P102" s="20"/>
-      <c r="Q102" s="20"/>
+      <c r="O102" s="20">
+        <v>15</v>
+      </c>
+      <c r="P102" s="20">
+        <v>10</v>
+      </c>
+      <c r="Q102" s="20">
+        <v>15</v>
+      </c>
       <c r="R102" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S102" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T102" s="18">
         <f t="shared" si="46"/>
@@ -14010,19 +14889,19 @@
       </c>
       <c r="X102" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y102" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z102" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA102" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB102" s="8">
         <v>39.270000000000003</v>
@@ -14035,14 +14914,14 @@
       </c>
       <c r="AE102" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>2905.6</v>
       </c>
       <c r="AF102" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG102" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>188.864</v>
       </c>
       <c r="AH102" s="64">
         <f t="shared" si="60"/>
@@ -14050,53 +14929,78 @@
       </c>
       <c r="AI102" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>2716.7359999999999</v>
       </c>
       <c r="AJ102" s="5">
         <v>0.18</v>
       </c>
       <c r="AK102" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>489.01247999999998</v>
       </c>
       <c r="AL102" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>3205.7484799999997</v>
       </c>
       <c r="AP102" s="12"/>
     </row>
     <row r="103" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A103" s="71"/>
-      <c r="B103" s="72"/>
-      <c r="C103" s="74"/>
-      <c r="D103" s="74"/>
-      <c r="E103" s="62"/>
-      <c r="F103" s="73"/>
-      <c r="G103" s="76"/>
-      <c r="H103" s="73"/>
-      <c r="I103" s="62"/>
-      <c r="J103" s="55"/>
-      <c r="K103" s="20"/>
+      <c r="A103" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B103" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C103" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.99044488765522176</v>
+      </c>
+      <c r="D103" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E103" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F103" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G103" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="H103" s="73" t="s">
+        <v>179</v>
+      </c>
+      <c r="I103" s="62" t="s">
+        <v>211</v>
+      </c>
+      <c r="J103" s="55">
+        <v>24</v>
+      </c>
+      <c r="K103" s="20">
+        <v>12</v>
+      </c>
       <c r="L103" s="20"/>
       <c r="M103" s="18"/>
       <c r="N103" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O103" s="18"/>
       <c r="P103" s="18"/>
-      <c r="Q103" s="18"/>
+      <c r="Q103" s="18">
+        <v>20</v>
+      </c>
       <c r="R103" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S103" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="T103" s="18">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U103" s="18">
         <f t="shared" si="47"/>
@@ -14108,7 +15012,7 @@
       </c>
       <c r="W103" s="8">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X103" s="18">
         <f t="shared" si="49"/>
@@ -14120,11 +15024,11 @@
       </c>
       <c r="Z103" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA103" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB103" s="8">
         <v>39.270000000000003</v>
@@ -14137,47 +15041,68 @@
       </c>
       <c r="AE103" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>5639.87</v>
       </c>
       <c r="AF103" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG103" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>366.59154999999998</v>
       </c>
       <c r="AH103" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>32.986800000000002</v>
       </c>
       <c r="AI103" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>5273.2784499999998</v>
       </c>
       <c r="AJ103" s="5">
         <v>0.18</v>
       </c>
       <c r="AK103" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>949.19012099999998</v>
       </c>
       <c r="AL103" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>6222.4685709999994</v>
       </c>
       <c r="AP103" s="12"/>
     </row>
     <row r="104" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A104" s="71"/>
-      <c r="B104" s="72"/>
-      <c r="C104" s="74"/>
-      <c r="D104" s="74"/>
-      <c r="E104" s="62"/>
-      <c r="F104" s="73"/>
-      <c r="G104" s="76"/>
-      <c r="H104" s="73"/>
-      <c r="I104" s="62"/>
-      <c r="J104" s="55"/>
+      <c r="A104" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B104" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C104" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.94672827243095925</v>
+      </c>
+      <c r="D104" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E104" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F104" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G104" s="76" t="s">
+        <v>206</v>
+      </c>
+      <c r="H104" s="73" t="s">
+        <v>179</v>
+      </c>
+      <c r="I104" s="62" t="s">
+        <v>211</v>
+      </c>
+      <c r="J104" s="55">
+        <v>40</v>
+      </c>
       <c r="K104" s="20"/>
       <c r="L104" s="20"/>
       <c r="M104" s="18"/>
@@ -14194,7 +15119,7 @@
       </c>
       <c r="S104" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T104" s="18">
         <f t="shared" si="46"/>
@@ -14239,72 +15164,99 @@
       </c>
       <c r="AE104" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>4476.3999999999996</v>
       </c>
       <c r="AF104" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG104" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>290.96600000000001</v>
       </c>
       <c r="AH104" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI104" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>4185.4339999999993</v>
       </c>
       <c r="AJ104" s="5">
         <v>0.18</v>
       </c>
       <c r="AK104" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>753.37811999999985</v>
       </c>
       <c r="AL104" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>4938.8121199999987</v>
       </c>
       <c r="AP104" s="12"/>
     </row>
     <row r="105" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A105" s="71"/>
-      <c r="B105" s="72"/>
-      <c r="C105" s="74"/>
-      <c r="D105" s="74"/>
-      <c r="E105" s="62"/>
-      <c r="F105" s="73"/>
-      <c r="G105" s="76"/>
-      <c r="H105" s="73"/>
-      <c r="I105" s="62"/>
+      <c r="A105" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B105" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C105" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.93135286872267797</v>
+      </c>
+      <c r="D105" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E105" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F105" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G105" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="H105" s="73" t="s">
+        <v>179</v>
+      </c>
+      <c r="I105" s="62" t="s">
+        <v>211</v>
+      </c>
       <c r="J105" s="55"/>
-      <c r="K105" s="18"/>
-      <c r="L105" s="18"/>
+      <c r="K105" s="18">
+        <v>10</v>
+      </c>
+      <c r="L105" s="18">
+        <v>5</v>
+      </c>
       <c r="M105" s="18"/>
       <c r="N105" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O105" s="18"/>
-      <c r="P105" s="18"/>
-      <c r="Q105" s="18"/>
+      <c r="P105" s="18">
+        <v>10</v>
+      </c>
+      <c r="Q105" s="18">
+        <v>10</v>
+      </c>
       <c r="R105" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S105" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="T105" s="18">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U105" s="18">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V105" s="18">
         <f t="shared" si="48"/>
@@ -14312,7 +15264,7 @@
       </c>
       <c r="W105" s="8">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X105" s="18">
         <f t="shared" si="49"/>
@@ -14320,15 +15272,15 @@
       </c>
       <c r="Y105" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z105" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA105" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB105" s="8">
         <v>39.270000000000003</v>
@@ -14341,14 +15293,14 @@
       </c>
       <c r="AE105" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>3329.3375000000001</v>
       </c>
       <c r="AF105" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG105" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>216.40693750000003</v>
       </c>
       <c r="AH105" s="64">
         <f t="shared" si="60"/>
@@ -14356,31 +15308,50 @@
       </c>
       <c r="AI105" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>3112.9305625000002</v>
       </c>
       <c r="AJ105" s="5">
         <v>0.18</v>
       </c>
       <c r="AK105" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>560.32750124999995</v>
       </c>
       <c r="AL105" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>3673.25806375</v>
       </c>
       <c r="AP105" s="12"/>
     </row>
     <row r="106" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A106" s="71"/>
-      <c r="B106" s="72"/>
-      <c r="C106" s="74"/>
-      <c r="D106" s="74"/>
-      <c r="E106" s="62"/>
-      <c r="F106" s="75"/>
-      <c r="G106" s="77"/>
-      <c r="H106" s="75"/>
-      <c r="I106" s="78"/>
+      <c r="A106" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B106" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C106" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.36136777618286686</v>
+      </c>
+      <c r="D106" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E106" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F106" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G106" s="77" t="s">
+        <v>208</v>
+      </c>
+      <c r="H106" s="73" t="s">
+        <v>179</v>
+      </c>
+      <c r="I106" s="62" t="s">
+        <v>211</v>
+      </c>
       <c r="J106" s="55"/>
       <c r="K106" s="69"/>
       <c r="L106" s="69"/>
@@ -14389,16 +15360,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O106" s="69"/>
-      <c r="P106" s="69"/>
-      <c r="Q106" s="69"/>
+      <c r="O106" s="69">
+        <v>12</v>
+      </c>
+      <c r="P106" s="69">
+        <v>18</v>
+      </c>
+      <c r="Q106" s="69">
+        <v>12</v>
+      </c>
       <c r="R106" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="S106" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="T106" s="18">
         <f t="shared" si="46"/>
@@ -14418,19 +15395,19 @@
       </c>
       <c r="X106" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Y106" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z106" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA106" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB106" s="8">
         <v>39.270000000000003</v>
@@ -14443,14 +15420,14 @@
       </c>
       <c r="AE106" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>3050.88</v>
       </c>
       <c r="AF106" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG106" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>198.30720000000002</v>
       </c>
       <c r="AH106" s="64">
         <f t="shared" si="60"/>
@@ -14458,38 +15435,61 @@
       </c>
       <c r="AI106" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>2852.5727999999999</v>
       </c>
       <c r="AJ106" s="5">
         <v>0.18</v>
       </c>
       <c r="AK106" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>513.46310399999993</v>
       </c>
       <c r="AL106" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>3366.0359039999998</v>
       </c>
       <c r="AP106" s="12"/>
     </row>
     <row r="107" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A107" s="71"/>
-      <c r="B107" s="72"/>
-      <c r="C107" s="74"/>
-      <c r="D107" s="74"/>
-      <c r="E107" s="62"/>
-      <c r="F107" s="73"/>
-      <c r="G107" s="76"/>
-      <c r="H107" s="73"/>
-      <c r="I107" s="62"/>
+      <c r="A107" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B107" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C107" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.1142353022554653</v>
+      </c>
+      <c r="D107" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E107" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F107" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G107" s="76" t="s">
+        <v>206</v>
+      </c>
+      <c r="H107" s="73" t="s">
+        <v>179</v>
+      </c>
+      <c r="I107" s="62" t="s">
+        <v>211</v>
+      </c>
       <c r="J107" s="55"/>
-      <c r="K107" s="20"/>
-      <c r="L107" s="20"/>
+      <c r="K107" s="20">
+        <v>12</v>
+      </c>
+      <c r="L107" s="20">
+        <v>12</v>
+      </c>
       <c r="M107" s="20"/>
       <c r="N107" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O107" s="18"/>
       <c r="P107" s="18"/>
@@ -14500,15 +15500,15 @@
       </c>
       <c r="S107" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T107" s="18">
         <f t="shared" ref="T107" si="64">K107/10</f>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U107" s="18">
         <f t="shared" ref="U107" si="65">L107/10</f>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V107" s="18">
         <f t="shared" ref="V107" si="66">M107/10</f>
@@ -14516,7 +15516,7 @@
       </c>
       <c r="W107" s="8">
         <f t="shared" ref="W107" si="67">N107/10</f>
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X107" s="18">
         <f t="shared" ref="X107" si="68">O107/10</f>
@@ -14545,14 +15545,14 @@
       </c>
       <c r="AE107" s="9">
         <f t="shared" ref="AE107" si="72">(J107*AB107)+(N107*AC107)+(AD107*S107)</f>
-        <v>0</v>
+        <v>3002.46</v>
       </c>
       <c r="AF107" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG107" s="10">
         <f t="shared" ref="AG107" si="73">AE107*AF107</f>
-        <v>0</v>
+        <v>195.15990000000002</v>
       </c>
       <c r="AH107" s="64">
         <f t="shared" ref="AH107" si="74">(AB107*J107)*$AH$1</f>
@@ -14560,57 +15560,82 @@
       </c>
       <c r="AI107" s="9">
         <f t="shared" ref="AI107" si="75">AE107-AG107</f>
-        <v>0</v>
+        <v>2807.3000999999999</v>
       </c>
       <c r="AJ107" s="5">
         <v>0.18</v>
       </c>
       <c r="AK107" s="11">
         <f t="shared" ref="AK107" si="76">AI107*AJ107</f>
-        <v>0</v>
+        <v>505.31401799999998</v>
       </c>
       <c r="AL107" s="9">
         <f t="shared" ref="AL107" si="77">AI107+AK107</f>
-        <v>0</v>
+        <v>3312.614118</v>
       </c>
       <c r="AP107" s="12"/>
     </row>
     <row r="108" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A108" s="71"/>
-      <c r="B108" s="72"/>
-      <c r="C108" s="74"/>
-      <c r="D108" s="74"/>
-      <c r="E108" s="62"/>
-      <c r="F108" s="73"/>
-      <c r="G108" s="76"/>
-      <c r="H108" s="73"/>
-      <c r="I108" s="62"/>
+      <c r="A108" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B108" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C108" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.20826447126501768</v>
+      </c>
+      <c r="D108" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E108" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F108" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G108" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H108" s="73" t="s">
+        <v>179</v>
+      </c>
+      <c r="I108" s="62" t="s">
+        <v>211</v>
+      </c>
       <c r="J108" s="55"/>
-      <c r="K108" s="18"/>
-      <c r="L108" s="18"/>
+      <c r="K108" s="18">
+        <v>40</v>
+      </c>
+      <c r="L108" s="18">
+        <v>40</v>
+      </c>
       <c r="M108" s="18"/>
       <c r="N108" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O108" s="18"/>
-      <c r="P108" s="18"/>
+      <c r="P108" s="18">
+        <v>40</v>
+      </c>
       <c r="Q108" s="18"/>
       <c r="R108" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S108" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="T108" s="18">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U108" s="18">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V108" s="18">
         <f t="shared" si="48"/>
@@ -14618,7 +15643,7 @@
       </c>
       <c r="W108" s="8">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X108" s="18">
         <f t="shared" si="49"/>
@@ -14626,7 +15651,7 @@
       </c>
       <c r="Y108" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z108" s="18">
         <f t="shared" si="51"/>
@@ -14634,7 +15659,7 @@
       </c>
       <c r="AA108" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB108" s="8">
         <v>39.270000000000003</v>
@@ -14647,14 +15672,14 @@
       </c>
       <c r="AE108" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>12913.8</v>
       </c>
       <c r="AF108" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG108" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>839.39699999999993</v>
       </c>
       <c r="AH108" s="64">
         <f t="shared" si="60"/>
@@ -14662,32 +15687,53 @@
       </c>
       <c r="AI108" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>12074.402999999998</v>
       </c>
       <c r="AJ108" s="5">
         <v>0.18</v>
       </c>
       <c r="AK108" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>2173.3925399999998</v>
       </c>
       <c r="AL108" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>14247.795539999999</v>
       </c>
       <c r="AP108" s="12"/>
     </row>
     <row r="109" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A109" s="71"/>
-      <c r="B109" s="72"/>
-      <c r="C109" s="74"/>
-      <c r="D109" s="74"/>
-      <c r="E109" s="62"/>
-      <c r="F109" s="73"/>
-      <c r="G109" s="76"/>
-      <c r="H109" s="73"/>
-      <c r="I109" s="62"/>
-      <c r="J109" s="55"/>
+      <c r="A109" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B109" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C109" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.92768597912405959</v>
+      </c>
+      <c r="D109" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E109" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F109" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G109" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="H109" s="73" t="s">
+        <v>179</v>
+      </c>
+      <c r="I109" s="62" t="s">
+        <v>211</v>
+      </c>
+      <c r="J109" s="55">
+        <v>40</v>
+      </c>
       <c r="K109" s="18"/>
       <c r="L109" s="20"/>
       <c r="M109" s="18"/>
@@ -14695,16 +15741,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O109" s="20"/>
-      <c r="P109" s="20"/>
-      <c r="Q109" s="20"/>
+      <c r="O109" s="20">
+        <v>15</v>
+      </c>
+      <c r="P109" s="20">
+        <v>10</v>
+      </c>
+      <c r="Q109" s="20">
+        <v>15</v>
+      </c>
       <c r="R109" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S109" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T109" s="18">
         <f t="shared" si="46"/>
@@ -14724,19 +15776,19 @@
       </c>
       <c r="X109" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y109" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z109" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA109" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB109" s="8">
         <v>39.270000000000003</v>
@@ -14749,53 +15801,78 @@
       </c>
       <c r="AE109" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>7382</v>
       </c>
       <c r="AF109" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG109" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>479.83000000000004</v>
       </c>
       <c r="AH109" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI109" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>6902.17</v>
       </c>
       <c r="AJ109" s="5">
         <v>0.18</v>
       </c>
       <c r="AK109" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1242.3905999999999</v>
       </c>
       <c r="AL109" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>8144.5605999999998</v>
       </c>
       <c r="AP109" s="12"/>
     </row>
     <row r="110" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A110" s="71"/>
-      <c r="B110" s="72"/>
-      <c r="C110" s="74"/>
-      <c r="D110" s="74"/>
-      <c r="E110" s="62"/>
-      <c r="F110" s="73"/>
-      <c r="G110" s="76"/>
-      <c r="H110" s="73"/>
-      <c r="I110" s="62"/>
-      <c r="J110" s="55"/>
-      <c r="K110" s="20"/>
-      <c r="L110" s="18"/>
+      <c r="A110" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B110" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C110" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.40714490468866549</v>
+      </c>
+      <c r="D110" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E110" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F110" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="G110" s="76" t="s">
+        <v>212</v>
+      </c>
+      <c r="H110" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="I110" s="62" t="s">
+        <v>221</v>
+      </c>
+      <c r="J110" s="55">
+        <v>40</v>
+      </c>
+      <c r="K110" s="20">
+        <v>40</v>
+      </c>
+      <c r="L110" s="18">
+        <v>20</v>
+      </c>
       <c r="M110" s="20"/>
       <c r="N110" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O110" s="20"/>
       <c r="P110" s="20"/>
@@ -14806,15 +15883,15 @@
       </c>
       <c r="S110" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T110" s="18">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U110" s="18">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V110" s="18">
         <f t="shared" si="48"/>
@@ -14822,7 +15899,7 @@
       </c>
       <c r="W110" s="8">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X110" s="18">
         <f t="shared" si="49"/>
@@ -14851,47 +15928,68 @@
       </c>
       <c r="AE110" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>11982.55</v>
       </c>
       <c r="AF110" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG110" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>778.86574999999993</v>
       </c>
       <c r="AH110" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI110" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>11203.684249999998</v>
       </c>
       <c r="AJ110" s="5">
         <v>0.18</v>
       </c>
       <c r="AK110" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>2016.6631649999997</v>
       </c>
       <c r="AL110" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>13220.347414999998</v>
       </c>
       <c r="AP110" s="12"/>
     </row>
     <row r="111" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A111" s="71"/>
-      <c r="B111" s="72"/>
-      <c r="C111" s="74"/>
-      <c r="D111" s="74"/>
-      <c r="E111" s="62"/>
-      <c r="F111" s="73"/>
-      <c r="G111" s="76"/>
-      <c r="H111" s="73"/>
-      <c r="I111" s="62"/>
-      <c r="J111" s="55"/>
+      <c r="A111" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B111" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C111" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.73473179979006564</v>
+      </c>
+      <c r="D111" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E111" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F111" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G111" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="H111" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="I111" s="62" t="s">
+        <v>221</v>
+      </c>
+      <c r="J111" s="55">
+        <v>40</v>
+      </c>
       <c r="K111" s="20"/>
       <c r="L111" s="20"/>
       <c r="M111" s="20"/>
@@ -14899,16 +15997,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O111" s="18"/>
-      <c r="P111" s="18"/>
-      <c r="Q111" s="18"/>
+      <c r="O111" s="18">
+        <v>6</v>
+      </c>
+      <c r="P111" s="18">
+        <v>6</v>
+      </c>
+      <c r="Q111" s="18">
+        <v>6</v>
+      </c>
       <c r="R111" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S111" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="T111" s="18">
         <f t="shared" si="46"/>
@@ -14928,19 +16032,19 @@
       </c>
       <c r="X111" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Y111" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Z111" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AA111" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB111" s="8">
         <v>39.270000000000003</v>
@@ -14953,46 +16057,65 @@
       </c>
       <c r="AE111" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>5783.92</v>
       </c>
       <c r="AF111" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG111" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>375.95480000000003</v>
       </c>
       <c r="AH111" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI111" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>5407.9651999999996</v>
       </c>
       <c r="AJ111" s="5">
         <v>0.18</v>
       </c>
       <c r="AK111" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>973.43373599999995</v>
       </c>
       <c r="AL111" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>6381.3989359999996</v>
       </c>
       <c r="AP111" s="12"/>
     </row>
     <row r="112" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A112" s="71"/>
-      <c r="B112" s="72"/>
-      <c r="C112" s="74"/>
-      <c r="D112" s="74"/>
-      <c r="E112" s="62"/>
-      <c r="F112" s="73"/>
-      <c r="G112" s="76"/>
-      <c r="H112" s="73"/>
-      <c r="I112" s="62"/>
+      <c r="A112" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B112" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C112" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>1.5259180914174442E-2</v>
+      </c>
+      <c r="D112" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E112" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F112" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G112" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H112" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="I112" s="62" t="s">
+        <v>221</v>
+      </c>
       <c r="J112" s="55"/>
       <c r="K112" s="18"/>
       <c r="L112" s="18"/>
@@ -15001,16 +16124,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O112" s="18"/>
-      <c r="P112" s="18"/>
-      <c r="Q112" s="18"/>
+      <c r="O112" s="18">
+        <v>80</v>
+      </c>
+      <c r="P112" s="18">
+        <v>80</v>
+      </c>
+      <c r="Q112" s="18">
+        <v>80</v>
+      </c>
       <c r="R112" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="S112" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="T112" s="18">
         <f t="shared" si="46"/>
@@ -15030,19 +16159,19 @@
       </c>
       <c r="X112" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y112" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z112" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA112" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB112" s="8">
         <v>39.270000000000003</v>
@@ -15055,14 +16184,14 @@
       </c>
       <c r="AE112" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>17433.599999999999</v>
       </c>
       <c r="AF112" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG112" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>1133.184</v>
       </c>
       <c r="AH112" s="64">
         <f t="shared" si="60"/>
@@ -15070,38 +16199,63 @@
       </c>
       <c r="AI112" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>16300.415999999999</v>
       </c>
       <c r="AJ112" s="5">
         <v>0.18</v>
       </c>
       <c r="AK112" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>2934.0748799999997</v>
       </c>
       <c r="AL112" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>19234.490879999998</v>
       </c>
       <c r="AP112" s="12"/>
     </row>
     <row r="113" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A113" s="71"/>
-      <c r="B113" s="72"/>
-      <c r="C113" s="74"/>
-      <c r="D113" s="74"/>
-      <c r="E113" s="62"/>
-      <c r="F113" s="73"/>
-      <c r="G113" s="76"/>
-      <c r="H113" s="73"/>
-      <c r="I113" s="62"/>
-      <c r="J113" s="55"/>
-      <c r="K113" s="18"/>
-      <c r="L113" s="18"/>
+      <c r="A113" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B113" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C113" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.20355355004952436</v>
+      </c>
+      <c r="D113" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E113" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F113" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G113" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="H113" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="I113" s="62" t="s">
+        <v>221</v>
+      </c>
+      <c r="J113" s="55">
+        <v>10</v>
+      </c>
+      <c r="K113" s="18">
+        <v>15</v>
+      </c>
+      <c r="L113" s="18">
+        <v>15</v>
+      </c>
       <c r="M113" s="18"/>
       <c r="N113" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O113" s="18"/>
       <c r="P113" s="18"/>
@@ -15112,15 +16266,15 @@
       </c>
       <c r="S113" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T113" s="18">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U113" s="18">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V113" s="18">
         <f t="shared" si="48"/>
@@ -15128,7 +16282,7 @@
       </c>
       <c r="W113" s="8">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X113" s="18">
         <f t="shared" si="49"/>
@@ -15157,46 +16311,65 @@
       </c>
       <c r="AE113" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>4872.1750000000002</v>
       </c>
       <c r="AF113" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG113" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>316.69137500000005</v>
       </c>
       <c r="AH113" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI113" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>4555.4836249999998</v>
       </c>
       <c r="AJ113" s="5">
         <v>0.18</v>
       </c>
       <c r="AK113" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>819.98705249999989</v>
       </c>
       <c r="AL113" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>5375.4706774999995</v>
       </c>
       <c r="AP113" s="12"/>
     </row>
     <row r="114" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A114" s="71"/>
-      <c r="B114" s="72"/>
-      <c r="C114" s="74"/>
-      <c r="D114" s="74"/>
-      <c r="E114" s="62"/>
-      <c r="F114" s="73"/>
-      <c r="G114" s="76"/>
-      <c r="H114" s="73"/>
-      <c r="I114" s="62"/>
+      <c r="A114" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B114" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C114" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.41840948335556083</v>
+      </c>
+      <c r="D114" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E114" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F114" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G114" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="H114" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="I114" s="62" t="s">
+        <v>221</v>
+      </c>
       <c r="J114" s="55"/>
       <c r="K114" s="18"/>
       <c r="L114" s="18"/>
@@ -15205,16 +16378,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O114" s="18"/>
-      <c r="P114" s="18"/>
-      <c r="Q114" s="18"/>
+      <c r="O114" s="18">
+        <v>6</v>
+      </c>
+      <c r="P114" s="18">
+        <v>6</v>
+      </c>
+      <c r="Q114" s="18">
+        <v>6</v>
+      </c>
       <c r="R114" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S114" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T114" s="18">
         <f t="shared" si="46"/>
@@ -15234,19 +16413,19 @@
       </c>
       <c r="X114" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Y114" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Z114" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AA114" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB114" s="8">
         <v>39.270000000000003</v>
@@ -15259,14 +16438,14 @@
       </c>
       <c r="AE114" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>1307.52</v>
       </c>
       <c r="AF114" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG114" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>84.988799999999998</v>
       </c>
       <c r="AH114" s="64">
         <f t="shared" si="60"/>
@@ -15274,57 +16453,88 @@
       </c>
       <c r="AI114" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>1222.5311999999999</v>
       </c>
       <c r="AJ114" s="5">
         <v>0.18</v>
       </c>
       <c r="AK114" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>220.05561599999999</v>
       </c>
       <c r="AL114" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>1442.586816</v>
       </c>
       <c r="AP114" s="12"/>
     </row>
     <row r="115" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A115" s="71"/>
-      <c r="B115" s="72"/>
-      <c r="C115" s="74"/>
-      <c r="D115" s="74"/>
-      <c r="E115" s="62"/>
-      <c r="F115" s="73"/>
-      <c r="G115" s="76"/>
-      <c r="H115" s="73"/>
-      <c r="I115" s="62"/>
-      <c r="J115" s="55"/>
-      <c r="K115" s="20"/>
-      <c r="L115" s="20"/>
+      <c r="A115" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B115" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C115" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.91260804540044549</v>
+      </c>
+      <c r="D115" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E115" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F115" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="G115" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H115" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="I115" s="62" t="s">
+        <v>221</v>
+      </c>
+      <c r="J115" s="55">
+        <v>40</v>
+      </c>
+      <c r="K115" s="20">
+        <v>40</v>
+      </c>
+      <c r="L115" s="20">
+        <v>40</v>
+      </c>
       <c r="M115" s="20"/>
       <c r="N115" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="O115" s="18"/>
-      <c r="P115" s="18"/>
-      <c r="Q115" s="20"/>
+        <v>80</v>
+      </c>
+      <c r="O115" s="18">
+        <v>40</v>
+      </c>
+      <c r="P115" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q115" s="20">
+        <v>40</v>
+      </c>
       <c r="R115" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S115" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="T115" s="18">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U115" s="18">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V115" s="18">
         <f t="shared" si="48"/>
@@ -15332,23 +16542,23 @@
       </c>
       <c r="W115" s="8">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X115" s="18">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y115" s="18">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z115" s="18">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA115" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB115" s="8">
         <v>39.270000000000003</v>
@@ -15361,46 +16571,65 @@
       </c>
       <c r="AE115" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>23201.399999999998</v>
       </c>
       <c r="AF115" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG115" s="10">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>1508.0909999999999</v>
       </c>
       <c r="AH115" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI115" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>21693.308999999997</v>
       </c>
       <c r="AJ115" s="5">
         <v>0.18</v>
       </c>
       <c r="AK115" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>3904.7956199999994</v>
       </c>
       <c r="AL115" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>25598.104619999998</v>
       </c>
       <c r="AP115" s="12"/>
     </row>
     <row r="116" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A116" s="71"/>
-      <c r="B116" s="72"/>
-      <c r="C116" s="74"/>
-      <c r="D116" s="74"/>
-      <c r="E116" s="62"/>
-      <c r="F116" s="73"/>
-      <c r="G116" s="76"/>
-      <c r="H116" s="73"/>
-      <c r="I116" s="62"/>
+      <c r="A116" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B116" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C116" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.80548975431334457</v>
+      </c>
+      <c r="D116" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E116" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F116" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G116" s="76" t="s">
+        <v>218</v>
+      </c>
+      <c r="H116" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="I116" s="62" t="s">
+        <v>221</v>
+      </c>
       <c r="J116" s="55"/>
       <c r="K116" s="18"/>
       <c r="L116" s="18"/>
@@ -15409,16 +16638,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O116" s="18"/>
-      <c r="P116" s="18"/>
-      <c r="Q116" s="18"/>
+      <c r="O116" s="18">
+        <v>6</v>
+      </c>
+      <c r="P116" s="18">
+        <v>6</v>
+      </c>
+      <c r="Q116" s="18">
+        <v>6</v>
+      </c>
       <c r="R116" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S116" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T116" s="18">
         <f t="shared" ref="T116:T172" si="78">K116/10</f>
@@ -15438,19 +16673,19 @@
       </c>
       <c r="X116" s="18">
         <f t="shared" ref="X116:X172" si="81">O116/10</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Y116" s="18">
         <f t="shared" ref="Y116:Y172" si="82">P116/10</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Z116" s="18">
         <f t="shared" ref="Z116:Z172" si="83">Q116/10</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AA116" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB116" s="8">
         <v>39.270000000000003</v>
@@ -15463,14 +16698,14 @@
       </c>
       <c r="AE116" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>1307.52</v>
       </c>
       <c r="AF116" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG116" s="10">
         <f t="shared" ref="AG116:AG172" si="84">AE116*AF116</f>
-        <v>0</v>
+        <v>84.988799999999998</v>
       </c>
       <c r="AH116" s="64">
         <f t="shared" si="60"/>
@@ -15478,32 +16713,53 @@
       </c>
       <c r="AI116" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>1222.5311999999999</v>
       </c>
       <c r="AJ116" s="5">
         <v>0.18</v>
       </c>
       <c r="AK116" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>220.05561599999999</v>
       </c>
       <c r="AL116" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>1442.586816</v>
       </c>
       <c r="AP116" s="12"/>
     </row>
     <row r="117" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A117" s="71"/>
-      <c r="B117" s="72"/>
-      <c r="C117" s="74"/>
-      <c r="D117" s="74"/>
-      <c r="E117" s="62"/>
-      <c r="F117" s="73"/>
-      <c r="G117" s="76"/>
-      <c r="H117" s="73"/>
-      <c r="I117" s="62"/>
-      <c r="J117" s="55"/>
+      <c r="A117" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B117" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C117" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.4141076703902018</v>
+      </c>
+      <c r="D117" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E117" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F117" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G117" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="H117" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="I117" s="62" t="s">
+        <v>221</v>
+      </c>
+      <c r="J117" s="55">
+        <v>12</v>
+      </c>
       <c r="K117" s="20"/>
       <c r="L117" s="20"/>
       <c r="M117" s="20"/>
@@ -15511,16 +16767,18 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O117" s="18"/>
+      <c r="O117" s="18">
+        <v>40</v>
+      </c>
       <c r="P117" s="18"/>
       <c r="Q117" s="20"/>
       <c r="R117" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S117" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="T117" s="18">
         <f t="shared" si="78"/>
@@ -15540,7 +16798,7 @@
       </c>
       <c r="X117" s="18">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y117" s="18">
         <f t="shared" si="82"/>
@@ -15552,7 +16810,7 @@
       </c>
       <c r="AA117" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB117" s="8">
         <v>39.270000000000003</v>
@@ -15565,47 +16823,68 @@
       </c>
       <c r="AE117" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>4248.5200000000004</v>
       </c>
       <c r="AF117" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG117" s="10">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>276.15380000000005</v>
       </c>
       <c r="AH117" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="AI117" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>3972.3662000000004</v>
       </c>
       <c r="AJ117" s="5">
         <v>0.18</v>
       </c>
       <c r="AK117" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>715.02591600000005</v>
       </c>
       <c r="AL117" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>4687.3921160000009</v>
       </c>
       <c r="AP117" s="12"/>
     </row>
     <row r="118" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A118" s="71"/>
-      <c r="B118" s="72"/>
-      <c r="C118" s="74"/>
-      <c r="D118" s="74"/>
-      <c r="E118" s="62"/>
-      <c r="F118" s="73"/>
-      <c r="G118" s="76"/>
-      <c r="H118" s="73"/>
-      <c r="I118" s="62"/>
-      <c r="J118" s="55"/>
+      <c r="A118" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B118" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C118" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.69103343727710576</v>
+      </c>
+      <c r="D118" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E118" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F118" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G118" s="76" t="s">
+        <v>220</v>
+      </c>
+      <c r="H118" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="I118" s="62" t="s">
+        <v>221</v>
+      </c>
+      <c r="J118" s="55">
+        <v>40</v>
+      </c>
       <c r="K118" s="20"/>
       <c r="L118" s="20"/>
       <c r="M118" s="20"/>
@@ -15613,16 +16892,18 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O118" s="18"/>
+      <c r="O118" s="18">
+        <v>40</v>
+      </c>
       <c r="P118" s="18"/>
       <c r="Q118" s="18"/>
       <c r="R118" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S118" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T118" s="18">
         <f t="shared" si="78"/>
@@ -15642,7 +16923,7 @@
       </c>
       <c r="X118" s="18">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y118" s="18">
         <f t="shared" si="82"/>
@@ -15654,7 +16935,7 @@
       </c>
       <c r="AA118" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB118" s="8">
         <v>39.270000000000003</v>
@@ -15667,46 +16948,65 @@
       </c>
       <c r="AE118" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>7382</v>
       </c>
       <c r="AF118" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG118" s="10">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>479.83000000000004</v>
       </c>
       <c r="AH118" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI118" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>6902.17</v>
       </c>
       <c r="AJ118" s="5">
         <v>0.18</v>
       </c>
       <c r="AK118" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1242.3905999999999</v>
       </c>
       <c r="AL118" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>8144.5605999999998</v>
       </c>
       <c r="AP118" s="12"/>
     </row>
     <row r="119" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A119" s="71"/>
-      <c r="B119" s="72"/>
-      <c r="C119" s="74"/>
-      <c r="D119" s="74"/>
-      <c r="E119" s="62"/>
-      <c r="F119" s="73"/>
-      <c r="G119" s="76"/>
-      <c r="H119" s="73"/>
-      <c r="I119" s="62"/>
+      <c r="A119" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B119" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C119" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>5.4398712620547518E-2</v>
+      </c>
+      <c r="D119" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E119" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F119" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G119" s="76" t="s">
+        <v>222</v>
+      </c>
+      <c r="H119" s="73" t="s">
+        <v>130</v>
+      </c>
+      <c r="I119" s="62" t="s">
+        <v>231</v>
+      </c>
       <c r="J119" s="55"/>
       <c r="K119" s="18"/>
       <c r="L119" s="18"/>
@@ -15715,16 +17015,18 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O119" s="20"/>
+      <c r="O119" s="20">
+        <v>12</v>
+      </c>
       <c r="P119" s="20"/>
       <c r="Q119" s="20"/>
       <c r="R119" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S119" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T119" s="18">
         <f t="shared" si="78"/>
@@ -15744,7 +17046,7 @@
       </c>
       <c r="X119" s="18">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Y119" s="18">
         <f t="shared" si="82"/>
@@ -15756,7 +17058,7 @@
       </c>
       <c r="AA119" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB119" s="8">
         <v>39.270000000000003</v>
@@ -15769,14 +17071,14 @@
       </c>
       <c r="AE119" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>871.68000000000006</v>
       </c>
       <c r="AF119" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG119" s="10">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>56.659200000000006</v>
       </c>
       <c r="AH119" s="64">
         <f t="shared" si="60"/>
@@ -15784,32 +17086,53 @@
       </c>
       <c r="AI119" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>815.02080000000001</v>
       </c>
       <c r="AJ119" s="5">
         <v>0.18</v>
       </c>
       <c r="AK119" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>146.703744</v>
       </c>
       <c r="AL119" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>961.72454400000004</v>
       </c>
       <c r="AP119" s="12"/>
     </row>
     <row r="120" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A120" s="71"/>
-      <c r="B120" s="72"/>
-      <c r="C120" s="74"/>
-      <c r="D120" s="74"/>
-      <c r="E120" s="62"/>
-      <c r="F120" s="73"/>
-      <c r="G120" s="76"/>
-      <c r="H120" s="73"/>
-      <c r="I120" s="62"/>
-      <c r="J120" s="55"/>
+      <c r="A120" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B120" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C120" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.65217676049550721</v>
+      </c>
+      <c r="D120" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E120" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F120" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="G120" s="76" t="s">
+        <v>198</v>
+      </c>
+      <c r="H120" s="73" t="s">
+        <v>130</v>
+      </c>
+      <c r="I120" s="62" t="s">
+        <v>231</v>
+      </c>
+      <c r="J120" s="55">
+        <v>10</v>
+      </c>
       <c r="K120" s="18"/>
       <c r="L120" s="18"/>
       <c r="M120" s="18"/>
@@ -15826,7 +17149,7 @@
       </c>
       <c r="S120" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T120" s="18">
         <f t="shared" si="78"/>
@@ -15871,53 +17194,74 @@
       </c>
       <c r="AE120" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>1119.0999999999999</v>
       </c>
       <c r="AF120" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG120" s="10">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>72.741500000000002</v>
       </c>
       <c r="AH120" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>13.744500000000002</v>
       </c>
       <c r="AI120" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>1046.3584999999998</v>
       </c>
       <c r="AJ120" s="5">
         <v>0.18</v>
       </c>
       <c r="AK120" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>188.34452999999996</v>
       </c>
       <c r="AL120" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>1234.7030299999997</v>
       </c>
       <c r="AP120" s="12"/>
     </row>
     <row r="121" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A121" s="71"/>
-      <c r="B121" s="72"/>
-      <c r="C121" s="74"/>
-      <c r="D121" s="74"/>
-      <c r="E121" s="62"/>
-      <c r="F121" s="73"/>
-      <c r="G121" s="76"/>
-      <c r="H121" s="73"/>
-      <c r="I121" s="62"/>
+      <c r="A121" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B121" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C121" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.57281810397993582</v>
+      </c>
+      <c r="D121" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E121" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F121" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G121" s="76" t="s">
+        <v>223</v>
+      </c>
+      <c r="H121" s="73" t="s">
+        <v>130</v>
+      </c>
+      <c r="I121" s="62" t="s">
+        <v>231</v>
+      </c>
       <c r="J121" s="55"/>
-      <c r="K121" s="20"/>
+      <c r="K121" s="20">
+        <v>10</v>
+      </c>
       <c r="L121" s="20"/>
       <c r="M121" s="20"/>
       <c r="N121" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O121" s="18"/>
       <c r="P121" s="18"/>
@@ -15928,11 +17272,11 @@
       </c>
       <c r="S121" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T121" s="18">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U121" s="18">
         <f t="shared" si="79"/>
@@ -15944,7 +17288,7 @@
       </c>
       <c r="W121" s="8">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X121" s="18">
         <f t="shared" si="81"/>
@@ -15973,14 +17317,14 @@
       </c>
       <c r="AE121" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>1251.0250000000001</v>
       </c>
       <c r="AF121" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG121" s="10">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>81.316625000000002</v>
       </c>
       <c r="AH121" s="64">
         <f t="shared" si="60"/>
@@ -15988,38 +17332,59 @@
       </c>
       <c r="AI121" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>1169.7083750000002</v>
       </c>
       <c r="AJ121" s="5">
         <v>0.18</v>
       </c>
       <c r="AK121" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>210.54750750000002</v>
       </c>
       <c r="AL121" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>1380.2558825000001</v>
       </c>
       <c r="AP121" s="12"/>
     </row>
     <row r="122" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A122" s="71"/>
-      <c r="B122" s="72"/>
-      <c r="C122" s="74"/>
-      <c r="D122" s="74"/>
-      <c r="E122" s="62"/>
-      <c r="F122" s="73"/>
-      <c r="G122" s="76"/>
-      <c r="H122" s="73"/>
-      <c r="I122" s="62"/>
+      <c r="A122" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B122" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C122" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.32584563781713727</v>
+      </c>
+      <c r="D122" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E122" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F122" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="G122" s="76" t="s">
+        <v>224</v>
+      </c>
+      <c r="H122" s="73" t="s">
+        <v>130</v>
+      </c>
+      <c r="I122" s="62" t="s">
+        <v>231</v>
+      </c>
       <c r="J122" s="55"/>
       <c r="K122" s="20"/>
-      <c r="L122" s="20"/>
+      <c r="L122" s="20">
+        <v>10</v>
+      </c>
       <c r="M122" s="20"/>
       <c r="N122" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O122" s="18"/>
       <c r="P122" s="18"/>
@@ -16030,7 +17395,7 @@
       </c>
       <c r="S122" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T122" s="18">
         <f t="shared" si="78"/>
@@ -16038,7 +17403,7 @@
       </c>
       <c r="U122" s="18">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V122" s="18">
         <f t="shared" si="80"/>
@@ -16046,7 +17411,7 @@
       </c>
       <c r="W122" s="8">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X122" s="18">
         <f t="shared" si="81"/>
@@ -16075,14 +17440,14 @@
       </c>
       <c r="AE122" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>1251.0250000000001</v>
       </c>
       <c r="AF122" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG122" s="10">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>81.316625000000002</v>
       </c>
       <c r="AH122" s="64">
         <f t="shared" si="60"/>
@@ -16090,31 +17455,50 @@
       </c>
       <c r="AI122" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>1169.7083750000002</v>
       </c>
       <c r="AJ122" s="5">
         <v>0.18</v>
       </c>
       <c r="AK122" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>210.54750750000002</v>
       </c>
       <c r="AL122" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>1380.2558825000001</v>
       </c>
       <c r="AP122" s="12"/>
     </row>
     <row r="123" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A123" s="71"/>
-      <c r="B123" s="72"/>
-      <c r="C123" s="74"/>
-      <c r="D123" s="74"/>
-      <c r="E123" s="62"/>
-      <c r="F123" s="73"/>
-      <c r="G123" s="76"/>
-      <c r="H123" s="73"/>
-      <c r="I123" s="62"/>
+      <c r="A123" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B123" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C123" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.46441415228615124</v>
+      </c>
+      <c r="D123" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E123" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F123" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G123" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="H123" s="73" t="s">
+        <v>130</v>
+      </c>
+      <c r="I123" s="62" t="s">
+        <v>231</v>
+      </c>
       <c r="J123" s="55"/>
       <c r="K123" s="20"/>
       <c r="L123" s="20"/>
@@ -16125,14 +17509,16 @@
       </c>
       <c r="O123" s="18"/>
       <c r="P123" s="18"/>
-      <c r="Q123" s="18"/>
+      <c r="Q123" s="18">
+        <v>10</v>
+      </c>
       <c r="R123" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S123" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T123" s="18">
         <f t="shared" si="78"/>
@@ -16160,11 +17546,11 @@
       </c>
       <c r="Z123" s="18">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA123" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB123" s="8">
         <v>39.270000000000003</v>
@@ -16177,14 +17563,14 @@
       </c>
       <c r="AE123" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>726.4</v>
       </c>
       <c r="AF123" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG123" s="10">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>47.216000000000001</v>
       </c>
       <c r="AH123" s="64">
         <f t="shared" si="60"/>
@@ -16192,31 +17578,50 @@
       </c>
       <c r="AI123" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>679.18399999999997</v>
       </c>
       <c r="AJ123" s="5">
         <v>0.18</v>
       </c>
       <c r="AK123" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>122.25312</v>
       </c>
       <c r="AL123" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>801.43711999999994</v>
       </c>
       <c r="AP123" s="12"/>
     </row>
     <row r="124" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A124" s="71"/>
-      <c r="B124" s="72"/>
-      <c r="C124" s="74"/>
-      <c r="D124" s="74"/>
-      <c r="E124" s="62"/>
-      <c r="F124" s="73"/>
-      <c r="G124" s="76"/>
-      <c r="H124" s="73"/>
-      <c r="I124" s="62"/>
+      <c r="A124" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B124" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C124" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.40826755471813359</v>
+      </c>
+      <c r="D124" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E124" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F124" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="G124" s="76" t="s">
+        <v>226</v>
+      </c>
+      <c r="H124" s="73" t="s">
+        <v>130</v>
+      </c>
+      <c r="I124" s="62" t="s">
+        <v>231</v>
+      </c>
       <c r="J124" s="55"/>
       <c r="K124" s="20"/>
       <c r="L124" s="20"/>
@@ -16225,16 +17630,18 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O124" s="18"/>
+      <c r="O124" s="18">
+        <v>10</v>
+      </c>
       <c r="P124" s="18"/>
       <c r="Q124" s="18"/>
       <c r="R124" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S124" s="18">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T124" s="18">
         <f t="shared" si="78"/>
@@ -16254,7 +17661,7 @@
       </c>
       <c r="X124" s="18">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y124" s="18">
         <f t="shared" si="82"/>
@@ -16266,7 +17673,7 @@
       </c>
       <c r="AA124" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB124" s="8">
         <v>39.270000000000003</v>
@@ -16279,14 +17686,14 @@
       </c>
       <c r="AE124" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>726.4</v>
       </c>
       <c r="AF124" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG124" s="10">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>47.216000000000001</v>
       </c>
       <c r="AH124" s="64">
         <f t="shared" si="60"/>
@@ -16294,31 +17701,50 @@
       </c>
       <c r="AI124" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>679.18399999999997</v>
       </c>
       <c r="AJ124" s="5">
         <v>0.18</v>
       </c>
       <c r="AK124" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>122.25312</v>
       </c>
       <c r="AL124" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>801.43711999999994</v>
       </c>
       <c r="AP124" s="12"/>
     </row>
     <row r="125" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A125" s="71"/>
-      <c r="B125" s="72"/>
-      <c r="C125" s="74"/>
-      <c r="D125" s="74"/>
-      <c r="E125" s="62"/>
-      <c r="F125" s="73"/>
-      <c r="G125" s="76"/>
-      <c r="H125" s="73"/>
-      <c r="I125" s="62"/>
+      <c r="A125" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B125" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C125" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.86609970959651272</v>
+      </c>
+      <c r="D125" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E125" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F125" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G125" s="76" t="s">
+        <v>227</v>
+      </c>
+      <c r="H125" s="73" t="s">
+        <v>130</v>
+      </c>
+      <c r="I125" s="62" t="s">
+        <v>231</v>
+      </c>
       <c r="J125" s="55"/>
       <c r="K125" s="18"/>
       <c r="L125" s="18"/>
@@ -16328,15 +17754,17 @@
         <v>0</v>
       </c>
       <c r="O125" s="18"/>
-      <c r="P125" s="18"/>
+      <c r="P125" s="18">
+        <v>10</v>
+      </c>
       <c r="Q125" s="18"/>
       <c r="R125" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S125" s="18">
         <f t="shared" ref="S125:S188" si="85">J125+K125+L125+M125+O125+P125+Q125</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T125" s="18">
         <f t="shared" si="78"/>
@@ -16360,7 +17788,7 @@
       </c>
       <c r="Y125" s="18">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z125" s="18">
         <f t="shared" si="83"/>
@@ -16368,7 +17796,7 @@
       </c>
       <c r="AA125" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB125" s="8">
         <v>39.270000000000003</v>
@@ -16381,14 +17809,14 @@
       </c>
       <c r="AE125" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>726.4</v>
       </c>
       <c r="AF125" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG125" s="10">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>47.216000000000001</v>
       </c>
       <c r="AH125" s="64">
         <f t="shared" si="60"/>
@@ -16396,32 +17824,53 @@
       </c>
       <c r="AI125" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>679.18399999999997</v>
       </c>
       <c r="AJ125" s="5">
         <v>0.18</v>
       </c>
       <c r="AK125" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>122.25312</v>
       </c>
       <c r="AL125" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>801.43711999999994</v>
       </c>
       <c r="AP125" s="12"/>
     </row>
     <row r="126" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A126" s="71"/>
-      <c r="B126" s="72"/>
-      <c r="C126" s="74"/>
-      <c r="D126" s="74"/>
-      <c r="E126" s="62"/>
-      <c r="F126" s="73"/>
-      <c r="G126" s="76"/>
-      <c r="H126" s="73"/>
-      <c r="I126" s="62"/>
-      <c r="J126" s="55"/>
+      <c r="A126" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B126" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C126" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.25865281842576804</v>
+      </c>
+      <c r="D126" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E126" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F126" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="G126" s="76" t="s">
+        <v>228</v>
+      </c>
+      <c r="H126" s="73" t="s">
+        <v>130</v>
+      </c>
+      <c r="I126" s="62" t="s">
+        <v>231</v>
+      </c>
+      <c r="J126" s="55">
+        <v>40</v>
+      </c>
       <c r="K126" s="18"/>
       <c r="L126" s="18"/>
       <c r="M126" s="20"/>
@@ -16429,16 +17878,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O126" s="18"/>
-      <c r="P126" s="18"/>
-      <c r="Q126" s="18"/>
+      <c r="O126" s="18">
+        <v>15</v>
+      </c>
+      <c r="P126" s="18">
+        <v>10</v>
+      </c>
+      <c r="Q126" s="18">
+        <v>15</v>
+      </c>
       <c r="R126" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S126" s="18">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T126" s="18">
         <f t="shared" si="78"/>
@@ -16458,19 +17913,19 @@
       </c>
       <c r="X126" s="18">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y126" s="18">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z126" s="18">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA126" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB126" s="8">
         <v>39.270000000000003</v>
@@ -16483,47 +17938,68 @@
       </c>
       <c r="AE126" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>7382</v>
       </c>
       <c r="AF126" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG126" s="10">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>479.83000000000004</v>
       </c>
       <c r="AH126" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>54.978000000000009</v>
       </c>
       <c r="AI126" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>6902.17</v>
       </c>
       <c r="AJ126" s="5">
         <v>0.18</v>
       </c>
       <c r="AK126" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1242.3905999999999</v>
       </c>
       <c r="AL126" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>8144.5605999999998</v>
       </c>
       <c r="AP126" s="12"/>
     </row>
     <row r="127" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A127" s="71"/>
-      <c r="B127" s="72"/>
-      <c r="C127" s="74"/>
-      <c r="D127" s="74"/>
-      <c r="E127" s="62"/>
-      <c r="F127" s="73"/>
-      <c r="G127" s="76"/>
-      <c r="H127" s="73"/>
-      <c r="I127" s="62"/>
-      <c r="J127" s="55"/>
+      <c r="A127" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B127" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C127" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.17445974672686904</v>
+      </c>
+      <c r="D127" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E127" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F127" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="G127" s="76" t="s">
+        <v>115</v>
+      </c>
+      <c r="H127" s="73" t="s">
+        <v>130</v>
+      </c>
+      <c r="I127" s="62" t="s">
+        <v>231</v>
+      </c>
+      <c r="J127" s="55">
+        <v>20</v>
+      </c>
       <c r="K127" s="18"/>
       <c r="L127" s="20"/>
       <c r="M127" s="18"/>
@@ -16533,14 +18009,16 @@
       </c>
       <c r="O127" s="20"/>
       <c r="P127" s="18"/>
-      <c r="Q127" s="18"/>
+      <c r="Q127" s="18">
+        <v>20</v>
+      </c>
       <c r="R127" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S127" s="18">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T127" s="18">
         <f t="shared" si="78"/>
@@ -16568,11 +18046,11 @@
       </c>
       <c r="Z127" s="18">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA127" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB127" s="8">
         <v>39.270000000000003</v>
@@ -16585,53 +18063,78 @@
       </c>
       <c r="AE127" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>3691</v>
       </c>
       <c r="AF127" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG127" s="10">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>239.91500000000002</v>
       </c>
       <c r="AH127" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>27.489000000000004</v>
       </c>
       <c r="AI127" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>3451.085</v>
       </c>
       <c r="AJ127" s="5">
         <v>0.18</v>
       </c>
       <c r="AK127" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>621.19529999999997</v>
       </c>
       <c r="AL127" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>4072.2802999999999</v>
       </c>
       <c r="AP127" s="12"/>
     </row>
     <row r="128" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A128" s="71"/>
-      <c r="B128" s="72"/>
-      <c r="C128" s="74"/>
-      <c r="D128" s="74"/>
-      <c r="E128" s="62"/>
-      <c r="F128" s="73"/>
-      <c r="G128" s="76"/>
-      <c r="H128" s="73"/>
-      <c r="I128" s="62"/>
-      <c r="J128" s="55"/>
-      <c r="K128" s="20"/>
-      <c r="L128" s="20"/>
+      <c r="A128" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B128" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C128" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.28855714485773742</v>
+      </c>
+      <c r="D128" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E128" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F128" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="G128" s="76" t="s">
+        <v>229</v>
+      </c>
+      <c r="H128" s="73" t="s">
+        <v>130</v>
+      </c>
+      <c r="I128" s="62" t="s">
+        <v>231</v>
+      </c>
+      <c r="J128" s="55">
+        <v>20</v>
+      </c>
+      <c r="K128" s="20">
+        <v>20</v>
+      </c>
+      <c r="L128" s="20">
+        <v>20</v>
+      </c>
       <c r="M128" s="20"/>
       <c r="N128" s="8">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O128" s="18"/>
       <c r="P128" s="20"/>
@@ -16642,15 +18145,15 @@
       </c>
       <c r="S128" s="18">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="T128" s="18">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U128" s="18">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V128" s="18">
         <f t="shared" si="80"/>
@@ -16658,7 +18161,7 @@
       </c>
       <c r="W128" s="8">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X128" s="18">
         <f t="shared" si="81"/>
@@ -16687,47 +18190,68 @@
       </c>
       <c r="AE128" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>7242.2999999999993</v>
       </c>
       <c r="AF128" s="21">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AG128" s="10">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>470.74949999999995</v>
       </c>
       <c r="AH128" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>27.489000000000004</v>
       </c>
       <c r="AI128" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>6771.5504999999994</v>
       </c>
       <c r="AJ128" s="5">
         <v>0.18</v>
       </c>
       <c r="AK128" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1218.8790899999999</v>
       </c>
       <c r="AL128" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>7990.4295899999997</v>
       </c>
       <c r="AP128" s="12"/>
     </row>
     <row r="129" spans="1:42" x14ac:dyDescent="0.35">
-      <c r="A129" s="71"/>
-      <c r="B129" s="72"/>
-      <c r="C129" s="74"/>
-      <c r="D129" s="74"/>
-      <c r="E129" s="62"/>
-      <c r="F129" s="73"/>
-      <c r="G129" s="76"/>
-      <c r="H129" s="73"/>
-      <c r="I129" s="62"/>
-      <c r="J129" s="55"/>
+      <c r="A129" s="71">
+        <v>46206</v>
+      </c>
+      <c r="B129" s="72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C129" s="103">
+        <f t="shared" ca="1" si="55"/>
+        <v>0.79569232946461466</v>
+      </c>
+      <c r="D129" s="73">
+        <v>6926.2</v>
+      </c>
+      <c r="E129" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F129" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="G129" s="76" t="s">
+        <v>230</v>
+      </c>
+      <c r="H129" s="73" t="s">
+        <v>130</v>
+      </c>
+      <c r="I129" s="62" t="s">
+        <v>231</v>
+      </c>
+      <c r="J129" s="55">
+        <v>80</v>
+      </c>
       <c r="K129" s="20"/>
       <c r="L129" s="20"/>
       <c r="M129" s="20"/>
@@ -16735,16 +18259,22 @@
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O129" s="20"/>
-      <c r="P129" s="18"/>
-      <c r="Q129" s="20"/>
+      <c r="O129" s="20">
+        <v>40</v>
+      </c>
+      <c r="P129" s="18">
+        <v>40</v>
+      </c>
+      <c r="Q129" s="20">
+        <v>40</v>
+      </c>
       <c r="R129" s="8">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="S129" s="18">
         <f t="shared" si="85"/>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T129" s="18">
         <f t="shared" si="78"/>
@@ -16764,19 +18294,19 @@
       </c>
       <c r="X129" s="18">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y129" s="18">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z129" s="18">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA129" s="8">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AB129" s="8">
         <v>39.270000000000003</v>
@@ -16789,33 +18319,33 @@
       </c>
       <c r="AE129" s="9">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>17669.599999999999</v>
       </c>
       <c r="AF129" s="21">
         <v>0.1</v>
       </c>
       <c r="AG129" s="10">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>1766.96</v>
       </c>
       <c r="AH129" s="64">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>109.95600000000002</v>
       </c>
       <c r="AI129" s="9">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>15902.64</v>
       </c>
       <c r="AJ129" s="5">
         <v>0.18</v>
       </c>
       <c r="AK129" s="11">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>2862.4751999999999</v>
       </c>
       <c r="AL129" s="9">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>18765.1152</v>
       </c>
       <c r="AP129" s="12"/>
     </row>
@@ -46803,15 +48333,15 @@
       <c r="I425" s="6"/>
       <c r="J425" s="6">
         <f t="shared" ref="J425:AA425" si="179">SUM(J3:J424)</f>
-        <v>1162</v>
+        <v>2390</v>
       </c>
       <c r="K425" s="6">
         <f t="shared" si="179"/>
-        <v>801</v>
+        <v>1102</v>
       </c>
       <c r="L425" s="6">
         <f t="shared" si="179"/>
-        <v>858</v>
+        <v>1128</v>
       </c>
       <c r="M425" s="6">
         <f t="shared" si="179"/>
@@ -46819,35 +48349,35 @@
       </c>
       <c r="N425" s="6">
         <f t="shared" si="179"/>
-        <v>1659</v>
+        <v>2230</v>
       </c>
       <c r="O425" s="6">
         <f t="shared" si="179"/>
-        <v>1026</v>
+        <v>1682</v>
       </c>
       <c r="P425" s="6">
         <f t="shared" si="179"/>
-        <v>1033</v>
+        <v>1660</v>
       </c>
       <c r="Q425" s="6">
         <f t="shared" si="179"/>
-        <v>1086</v>
+        <v>1852</v>
       </c>
       <c r="R425" s="6">
         <f>SUM(R3:R424)</f>
-        <v>3145</v>
+        <v>5194</v>
       </c>
       <c r="S425" s="6">
         <f>SUM(S3:S424)</f>
-        <v>5966</v>
+        <v>9814</v>
       </c>
       <c r="T425" s="6">
         <f t="shared" si="179"/>
-        <v>78.100000000000009</v>
+        <v>108.2</v>
       </c>
       <c r="U425" s="6">
         <f t="shared" si="179"/>
-        <v>83.800000000000011</v>
+        <v>110.80000000000001</v>
       </c>
       <c r="V425" s="6">
         <f t="shared" si="179"/>
@@ -46855,51 +48385,51 @@
       </c>
       <c r="W425" s="6">
         <f t="shared" si="179"/>
-        <v>161.90000000000003</v>
+        <v>219.00000000000003</v>
       </c>
       <c r="X425" s="6">
         <f t="shared" si="179"/>
-        <v>102.6</v>
+        <v>168.19999999999996</v>
       </c>
       <c r="Y425" s="6">
         <f t="shared" si="179"/>
-        <v>103.3</v>
+        <v>165.99999999999997</v>
       </c>
       <c r="Z425" s="6">
         <f t="shared" si="179"/>
-        <v>108.60000000000001</v>
+        <v>185.2</v>
       </c>
       <c r="AA425" s="6">
         <f t="shared" si="179"/>
-        <v>314.5</v>
+        <v>519.4</v>
       </c>
       <c r="AB425" s="6"/>
       <c r="AC425" s="6"/>
       <c r="AD425" s="6"/>
       <c r="AE425" s="6">
         <f>SUM(AE3:AE424)</f>
-        <v>566037.26749999973</v>
+        <v>923735.63500000036</v>
       </c>
       <c r="AF425" s="7"/>
       <c r="AG425" s="6">
         <f>SUM(AG3:AG424)</f>
-        <v>38494.828387499983</v>
+        <v>63246.463524999999</v>
       </c>
       <c r="AH425" s="6">
         <f>SUM(AH3:AH424)</f>
-        <v>1597.1109000000004</v>
+        <v>3284.935500000001</v>
       </c>
       <c r="AI425" s="6">
         <f>SUM(AI3:AI424)</f>
-        <v>527542.43911249994</v>
+        <v>860489.17147500021</v>
       </c>
       <c r="AK425" s="6">
         <f>SUM(AK3:AK424)</f>
-        <v>94957.63904025004</v>
+        <v>154888.05086550006</v>
       </c>
       <c r="AL425" s="6">
         <f>SUM(AL3:AL424)</f>
-        <v>622500.07815274969</v>
+        <v>1015377.2223404995</v>
       </c>
       <c r="AP425" s="12"/>
     </row>
@@ -46976,15 +48506,15 @@
       </c>
       <c r="J429" s="61">
         <f t="shared" ref="J429:AF429" si="180">+J425/40</f>
-        <v>29.05</v>
+        <v>59.75</v>
       </c>
       <c r="K429" s="62">
         <f t="shared" si="180"/>
-        <v>20.024999999999999</v>
+        <v>27.55</v>
       </c>
       <c r="L429" s="62">
         <f t="shared" si="180"/>
-        <v>21.45</v>
+        <v>28.2</v>
       </c>
       <c r="M429" s="62">
         <f t="shared" si="180"/>
@@ -46992,35 +48522,35 @@
       </c>
       <c r="N429" s="61">
         <f t="shared" si="180"/>
-        <v>41.475000000000001</v>
+        <v>55.75</v>
       </c>
       <c r="O429" s="62">
         <f t="shared" si="180"/>
-        <v>25.65</v>
+        <v>42.05</v>
       </c>
       <c r="P429" s="62">
         <f t="shared" si="180"/>
-        <v>25.824999999999999</v>
+        <v>41.5</v>
       </c>
       <c r="Q429" s="62">
         <f t="shared" si="180"/>
-        <v>27.15</v>
+        <v>46.3</v>
       </c>
       <c r="R429" s="61">
         <f t="shared" si="180"/>
-        <v>78.625</v>
+        <v>129.85</v>
       </c>
       <c r="S429" s="80">
         <f t="shared" si="180"/>
-        <v>149.15</v>
+        <v>245.35</v>
       </c>
       <c r="T429" s="80">
         <f t="shared" si="180"/>
-        <v>1.9525000000000001</v>
+        <v>2.7050000000000001</v>
       </c>
       <c r="U429" s="80">
         <f t="shared" si="180"/>
-        <v>2.0950000000000002</v>
+        <v>2.7700000000000005</v>
       </c>
       <c r="V429" s="80">
         <f t="shared" si="180"/>
@@ -47028,23 +48558,23 @@
       </c>
       <c r="W429" s="80">
         <f t="shared" si="180"/>
-        <v>4.0475000000000012</v>
+        <v>5.4750000000000005</v>
       </c>
       <c r="X429" s="80">
         <f t="shared" si="180"/>
-        <v>2.5649999999999999</v>
+        <v>4.2049999999999992</v>
       </c>
       <c r="Y429" s="80">
         <f t="shared" si="180"/>
-        <v>2.5825</v>
+        <v>4.1499999999999995</v>
       </c>
       <c r="Z429" s="80">
         <f t="shared" si="180"/>
-        <v>2.7150000000000003</v>
+        <v>4.63</v>
       </c>
       <c r="AA429" s="80">
         <f t="shared" si="180"/>
-        <v>7.8624999999999998</v>
+        <v>12.984999999999999</v>
       </c>
       <c r="AB429" s="81"/>
       <c r="AC429" s="57">
@@ -47057,7 +48587,7 @@
       </c>
       <c r="AE429" s="57">
         <f t="shared" si="180"/>
-        <v>14150.931687499993</v>
+        <v>23093.390875000008</v>
       </c>
       <c r="AF429" s="57">
         <f t="shared" si="180"/>
@@ -47077,7 +48607,7 @@
     <row r="431" spans="1:42" x14ac:dyDescent="0.35">
       <c r="S431" s="79">
         <f>S429+W429+AA429</f>
-        <v>161.06000000000003</v>
+        <v>263.81</v>
       </c>
       <c r="X431" t="s">
         <v>50</v>
@@ -47099,13 +48629,14 @@
     <filterColumn colId="25" showButton="0"/>
   </autoFilter>
   <mergeCells count="27">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AO1:AO2"/>
+    <mergeCell ref="AP1:AP2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AN2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -47118,14 +48649,13 @@
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AO1:AO2"/>
-    <mergeCell ref="AP1:AP2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AN2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -47197,11 +48727,11 @@
       </c>
       <c r="G7" s="29">
         <f>'STT Report'!Q429+'STT Report'!Z429</f>
-        <v>29.864999999999998</v>
+        <v>50.93</v>
       </c>
       <c r="H7" s="30">
         <f>E7+F7-G7</f>
-        <v>899.23500000000001</v>
+        <v>878.17000000000007</v>
       </c>
     </row>
     <row r="8" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -47216,11 +48746,11 @@
       </c>
       <c r="G8" s="29">
         <f>'STT Report'!P429+'STT Report'!Y429</f>
-        <v>28.407499999999999</v>
+        <v>45.65</v>
       </c>
       <c r="H8" s="30">
         <f>E8+F8-G8</f>
-        <v>650.6925</v>
+        <v>633.45000000000005</v>
       </c>
     </row>
     <row r="9" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -47235,11 +48765,11 @@
       </c>
       <c r="G9" s="29">
         <f>'STT Report'!O429+'STT Report'!X429</f>
-        <v>28.215</v>
+        <v>46.254999999999995</v>
       </c>
       <c r="H9" s="30">
         <f>E9+F9-G9</f>
-        <v>840.08499999999992</v>
+        <v>822.04499999999996</v>
       </c>
     </row>
     <row r="10" spans="4:8" x14ac:dyDescent="0.35">
@@ -47256,11 +48786,11 @@
       </c>
       <c r="G10" s="35">
         <f>SUM(G7:G9)</f>
-        <v>86.487499999999997</v>
+        <v>142.83499999999998</v>
       </c>
       <c r="H10" s="36">
         <f>SUM(H7:H9)</f>
-        <v>2390.0124999999998</v>
+        <v>2333.665</v>
       </c>
     </row>
     <row r="11" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -47275,11 +48805,11 @@
       </c>
       <c r="G11" s="58">
         <f>'STT Report'!J429</f>
-        <v>29.05</v>
+        <v>59.75</v>
       </c>
       <c r="H11" s="30">
         <f t="shared" ref="H11:H13" si="0">(E11+F11)-G11</f>
-        <v>1845.8500000000001</v>
+        <v>1815.15</v>
       </c>
     </row>
     <row r="12" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -47316,11 +48846,11 @@
       </c>
       <c r="G14" s="33">
         <f>SUM(G11:G13)</f>
-        <v>29.05</v>
+        <v>59.75</v>
       </c>
       <c r="H14" s="36">
         <f>SUM(H11:H13)</f>
-        <v>1845.8500000000001</v>
+        <v>1815.15</v>
       </c>
     </row>
     <row r="15" spans="4:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -47354,11 +48884,11 @@
       </c>
       <c r="G16" s="29">
         <f>'STT Report'!L429+'STT Report'!U429</f>
-        <v>23.544999999999998</v>
+        <v>30.97</v>
       </c>
       <c r="H16" s="30">
         <f>E16+F16-G16</f>
-        <v>610.45500000000004</v>
+        <v>603.03</v>
       </c>
     </row>
     <row r="17" spans="3:13" ht="16.5" x14ac:dyDescent="0.45">
@@ -47373,11 +48903,11 @@
       </c>
       <c r="G17" s="29">
         <f>'STT Report'!K429+'STT Report'!T429</f>
-        <v>21.977499999999999</v>
+        <v>30.255000000000003</v>
       </c>
       <c r="H17" s="30">
         <f>E17+F17-G17</f>
-        <v>606.72250000000008</v>
+        <v>598.44500000000005</v>
       </c>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.35">
@@ -47394,11 +48924,11 @@
       </c>
       <c r="G18" s="35">
         <f>SUM(G15:G17)</f>
-        <v>45.522499999999994</v>
+        <v>61.225000000000001</v>
       </c>
       <c r="H18" s="36">
         <f>SUM(H15:H17)</f>
-        <v>1602.2775000000001</v>
+        <v>1586.575</v>
       </c>
     </row>
     <row r="19" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -47415,11 +48945,11 @@
       </c>
       <c r="G19" s="38">
         <f>G10+G14+G18</f>
-        <v>161.06</v>
+        <v>263.81</v>
       </c>
       <c r="H19" s="40">
         <f>H10+H14+H18</f>
-        <v>5838.14</v>
+        <v>5735.39</v>
       </c>
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.35">
